--- a/EnergyScope_LCA-ANNE_20_02_25/case_studies/SA_FINAL_03-03-2025/2035_steamlow5/output/LCA_Construction_final.xlsx
+++ b/EnergyScope_LCA-ANNE_20_02_25/case_studies/SA_FINAL_03-03-2025/2035_steamlow5/output/LCA_Construction_final.xlsx
@@ -522,52 +522,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48726946427397e-05</v>
+        <v>0.8143940626745935</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007089999999999999</v>
+        <v>38.82318599999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1352153229716014</v>
+        <v>7404.075647075533</v>
       </c>
       <c r="E2" t="n">
-        <v>1.137736061927294e-06</v>
+        <v>0.06229977256856258</v>
       </c>
       <c r="F2" t="n">
-        <v>1.43123045047354e-06</v>
+        <v>0.07837084060310019</v>
       </c>
       <c r="G2" t="n">
-        <v>1.686065947331364e-05</v>
+        <v>0.9232503791468509</v>
       </c>
       <c r="H2" t="n">
-        <v>7.899853823721308e-12</v>
+        <v>4.325775661088061e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.698826224656809e-10</v>
+        <v>9.302376093304525e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000106782834196974</v>
+        <v>5.847178890883333</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02779017504483046</v>
+        <v>1521.725154778577</v>
       </c>
       <c r="L2" t="n">
-        <v>3.386525487226025e-07</v>
+        <v>0.01854382353798541</v>
       </c>
       <c r="M2" t="n">
-        <v>1.185730627986147e-10</v>
+        <v>6.492784304118899e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.758627466384517e-06</v>
+        <v>0.2605713388323764</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000581435960598733</v>
+        <v>31.83807679183819</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009107205915883518</v>
+        <v>498.6893500883584</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.721718992079524e-11</v>
+        <v>3.680656511554808e-06</v>
       </c>
     </row>
     <row r="3">
@@ -577,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3995616332409404</v>
+        <v>1.048850115849063e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>19.04760399999996</v>
+        <v>5e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3632.620488991763</v>
+        <v>0.0009535636316756091</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03056579120466931</v>
+        <v>8.023526529811671e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03845065000474122</v>
+        <v>1.009330359995444e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4529692028582873</v>
+        <v>1.189045096848634e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.122331273513718e-07</v>
+        <v>5.571123994161478e-14</v>
       </c>
       <c r="I3" t="n">
-        <v>4.563973087739157e-06</v>
+        <v>1.198043881986198e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>2.868768885446566</v>
+        <v>7.53052427341143e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>746.5955561983245</v>
+        <v>0.0001959814883274364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009098053091197213</v>
+        <v>2.388240823149524e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.185518681601041e-06</v>
+        <v>8.361993145177339e-13</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1278426679311924</v>
+        <v>3.35587268433323e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>15.62053868666323</v>
+        <v>4.100394644560877e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>244.6691845306152</v>
+        <v>6.422571167759887e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.805820050217346e-06</v>
+        <v>4.740281376642832e-13</v>
       </c>
     </row>
     <row r="4">
@@ -632,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001853193042811868</v>
+        <v>3.502031191421571e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02435799999999533</v>
+        <v>0.004603</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6242844397998984</v>
+        <v>0.1179727923638839</v>
       </c>
       <c r="E4" t="n">
-        <v>3.234730423648183e-06</v>
+        <v>6.112761367951162e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.193726796055302e-05</v>
+        <v>9.814732097153761e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006358707157108099</v>
+        <v>0.0001201622836200599</v>
       </c>
       <c r="H4" t="n">
-        <v>2.461920536076724e-11</v>
+        <v>4.652360714165091e-12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.939635928256712e-10</v>
+        <v>5.555112972234271e-11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00265927754116681</v>
+        <v>0.0005025311816238268</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09710682474854836</v>
+        <v>0.01835055071506912</v>
       </c>
       <c r="L4" t="n">
-        <v>3.873842768545658e-07</v>
+        <v>7.320510002306874e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.364131676242405e-09</v>
+        <v>2.577838125357169e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001075001449346998</v>
+        <v>2.031460576133171e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01316732628976603</v>
+        <v>0.002488266808104304</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4427446391265539</v>
+        <v>0.08366670391246893</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.467768987807193e-09</v>
+        <v>4.663412698447609e-10</v>
       </c>
     </row>
     <row r="5">
@@ -687,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.097700231698126e-07</v>
+        <v>4.195400463396252e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001907127263351219</v>
+        <v>0.0003814254526702438</v>
       </c>
       <c r="E5" t="n">
-        <v>1.604705305962334e-08</v>
+        <v>3.209410611924666e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>2.018660719990885e-08</v>
+        <v>4.037321439981771e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>2.37809019369727e-07</v>
+        <v>4.756180387394539e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.114224798832341e-13</v>
+        <v>2.228449597664682e-14</v>
       </c>
       <c r="I5" t="n">
-        <v>2.396087763972911e-12</v>
+        <v>4.792175527945822e-13</v>
       </c>
       <c r="J5" t="n">
-        <v>1.506104854682287e-06</v>
+        <v>3.012209709364573e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000391962976654873</v>
+        <v>7.839259533097459e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.776481646299051e-09</v>
+        <v>9.5529632925981e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>1.672398629035469e-12</v>
+        <v>3.344797258070938e-13</v>
       </c>
       <c r="N5" t="n">
-        <v>6.71174536866646e-08</v>
+        <v>1.342349073733292e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>8.200789289121765e-06</v>
+        <v>1.640157857824353e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001284514233551978</v>
+        <v>2.569028467103955e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.480562753285658e-13</v>
+        <v>1.896112550657131e-13</v>
       </c>
     </row>
     <row r="6">
@@ -742,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.235871789647704e-08</v>
+        <v>4.471743579295407e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>5e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000126683055618122</v>
+        <v>2.53366111236244e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>7.94435603949301e-10</v>
+        <v>1.588871207898602e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.524137737812955e-09</v>
+        <v>1.304827547562591e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>6.396972703132027e-08</v>
+        <v>1.279394540626405e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.274250587646546e-14</v>
+        <v>2.548501175293091e-15</v>
       </c>
       <c r="I6" t="n">
-        <v>1.117251535818377e-13</v>
+        <v>2.234503071636753e-14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.580521052569664e-07</v>
+        <v>5.161042105139326e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.755674562082005e-05</v>
+        <v>1.351134912416401e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.009230076993284e-10</v>
+        <v>2.018460153986567e-11</v>
       </c>
       <c r="M6" t="n">
-        <v>4.284044646124353e-13</v>
+        <v>8.568089292248704e-14</v>
       </c>
       <c r="N6" t="n">
-        <v>1.818524530491184e-08</v>
+        <v>3.637049060982367e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.368167534703878e-06</v>
+        <v>4.736335069407754e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>5.85376129844782e-05</v>
+        <v>1.170752259689564e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.054572721136778e-12</v>
+        <v>2.109145442273554e-13</v>
       </c>
     </row>
     <row r="7">
@@ -797,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.154662514822841e-06</v>
+        <v>1.776403868958217e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007704362886696545</v>
+        <v>0.001185286597953315</v>
       </c>
       <c r="E7" t="n">
-        <v>6.255057560916808e-08</v>
+        <v>9.623165478333552e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.183021923262573e-07</v>
+        <v>1.820033728096266e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.145116865060335e-06</v>
+        <v>1.761718253938978e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>8.071651884666448e-13</v>
+        <v>1.241792597640992e-13</v>
       </c>
       <c r="I7" t="n">
-        <v>1.067765250413412e-11</v>
+        <v>1.642715769866788e-12</v>
       </c>
       <c r="J7" t="n">
-        <v>1.806195345428094e-05</v>
+        <v>2.778762069889377e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000842492380221322</v>
+        <v>0.0001296142123417419</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372161003236359e-08</v>
+        <v>3.649478466517476e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>8.597927598445269e-12</v>
+        <v>1.322758092068503e-12</v>
       </c>
       <c r="N7" t="n">
-        <v>3.239197523529579e-07</v>
+        <v>4.983380805430122e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002882798429385799</v>
+        <v>4.435074506747384e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001071396953395481</v>
+        <v>0.0001648303005223818</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.843333829113029e-12</v>
+        <v>1.514359050632774e-12</v>
       </c>
     </row>
     <row r="8">
@@ -907,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.083330671924566e-07</v>
+        <v>1.048850115849063e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005530669063718532</v>
+        <v>0.0009535636316756089</v>
       </c>
       <c r="E9" t="n">
-        <v>4.653645387290769e-08</v>
+        <v>8.023526529811671e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>5.854116087973577e-08</v>
+        <v>1.009330359995444e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.896461561722068e-07</v>
+        <v>1.189045096848633e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.231251916613719e-13</v>
+        <v>5.571123994161586e-14</v>
       </c>
       <c r="I9" t="n">
-        <v>6.948654515520658e-12</v>
+        <v>1.19804388198632e-12</v>
       </c>
       <c r="J9" t="n">
-        <v>4.367704078578627e-06</v>
+        <v>7.530524273411427e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001136692632299131</v>
+        <v>0.0001959814883274363</v>
       </c>
       <c r="L9" t="n">
-        <v>1.385179677426724e-08</v>
+        <v>2.388240823149524e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>4.849956024202857e-12</v>
+        <v>8.36199314517734e-13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.946406156913272e-07</v>
+        <v>3.355872684333228e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.378228893845313e-05</v>
+        <v>4.100394644560884e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003725091277300734</v>
+        <v>6.422571167759887e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74936319845284e-12</v>
+        <v>4.740281376642828e-13</v>
       </c>
     </row>
     <row r="10">
@@ -962,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.068201074257999e-05</v>
+        <v>0.01008365639037845</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001651</v>
+        <v>1.55851899999998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07464692942981525</v>
+        <v>70.46557105271036</v>
       </c>
       <c r="E10" t="n">
-        <v>6.023041096203395e-07</v>
+        <v>0.0005685659591892007</v>
       </c>
       <c r="F10" t="n">
-        <v>2.606304709391637e-06</v>
+        <v>0.002460312180118894</v>
       </c>
       <c r="G10" t="n">
-        <v>2.545621044596196e-05</v>
+        <v>0.0240302771944456</v>
       </c>
       <c r="H10" t="n">
-        <v>1.233406922123525e-11</v>
+        <v>1.164317457820116e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>1.746178955822969e-10</v>
+        <v>1.648366493064945e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>8.250154160244626e-05</v>
+        <v>0.07788020600648174</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05843766311004805</v>
+        <v>55.16426909303928</v>
       </c>
       <c r="L10" t="n">
-        <v>9.133589482538639e-08</v>
+        <v>8.62197016761748e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.804933170189591e-10</v>
+        <v>2.647814439412875e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>8.295498028191133e-06</v>
+        <v>0.007830824525377502</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0007445659786990091</v>
+        <v>0.7028590094221602</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01687024252273683</v>
+        <v>15.92525348654934</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.595252812840124e-10</v>
+        <v>1.505894499463808e-07</v>
       </c>
     </row>
     <row r="11">
@@ -1017,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1278925724226915</v>
+        <v>0.1270611797662741</v>
       </c>
       <c r="C11" t="n">
-        <v>13.334849</v>
+        <v>13.24816299999999</v>
       </c>
       <c r="D11" t="n">
-        <v>669.1502516630139</v>
+        <v>664.8002992401808</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005434961004269532</v>
+        <v>0.005399629893312359</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03111794310994962</v>
+        <v>0.03091565435389177</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3181270111145696</v>
+        <v>0.3160589593439437</v>
       </c>
       <c r="H11" t="n">
-        <v>4.745541186620259e-08</v>
+        <v>4.714691794677134e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>7.772832673562878e-07</v>
+        <v>7.722303734454493e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7265007453686364</v>
+        <v>0.7217779739586992</v>
       </c>
       <c r="K11" t="n">
-        <v>1698.7092653203</v>
+        <v>1687.666447259626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0008776301109636316</v>
+        <v>0.0008719248912195612</v>
       </c>
       <c r="M11" t="n">
-        <v>2.466210617911704e-06</v>
+        <v>2.450178495341415e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09326546199695206</v>
+        <v>0.09265917017927432</v>
       </c>
       <c r="O11" t="n">
-        <v>5.288525731206649</v>
+        <v>5.254146553644502</v>
       </c>
       <c r="P11" t="n">
-        <v>137.1388409164802</v>
+        <v>136.2473409404634</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.222696222639151e-06</v>
+        <v>1.214747827816254e-06</v>
       </c>
     </row>
     <row r="12">
@@ -1072,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>8.262177894979757e-09</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4.949893509695352e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4.527414939151695e-10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.39753317841359e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.193779380888963e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5.085973100131748e-15</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.44279209514962e-14</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4.625730355422399e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.15255363429082e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.396863820398997e-11</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.204704950361928e-13</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.075920995233273e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5.291298379719497e-07</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.049540984365992e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.087160790437112e-14</v>
       </c>
     </row>
     <row r="13">
@@ -1127,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1634669004759482</v>
+        <v>0.1634668839515924</v>
       </c>
       <c r="C13" t="n">
-        <v>19.784965</v>
+        <v>19.784963</v>
       </c>
       <c r="D13" t="n">
-        <v>979.334698430497</v>
+        <v>979.334599432627</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00895747461115934</v>
+        <v>0.008957473705676355</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02765014502125164</v>
+        <v>0.02765014222618529</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2361888326860981</v>
+        <v>0.2361888088105105</v>
       </c>
       <c r="H13" t="n">
-        <v>1.006257997770481e-07</v>
+        <v>1.006257896051019e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>1.076854511048119e-06</v>
+        <v>1.076854402192277e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9151991318146973</v>
+        <v>0.9151990393000903</v>
       </c>
       <c r="K13" t="n">
-        <v>228.0323331506667</v>
+        <v>228.032310099594</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0008699179679636043</v>
+        <v>0.0008699178800263281</v>
       </c>
       <c r="M13" t="n">
-        <v>2.383504527823747e-06</v>
+        <v>2.383504286882758e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4107202423345546</v>
+        <v>0.4107202008161348</v>
       </c>
       <c r="O13" t="n">
-        <v>10.4688153247307</v>
+        <v>10.46881426647102</v>
       </c>
       <c r="P13" t="n">
-        <v>207.6513164174669</v>
+        <v>207.6512954266473</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.204342631881706e-06</v>
+        <v>1.20434251013849e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1182,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>8.262177894979757e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4.949893509695352e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4.527414939151695e-10</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.39753317841359e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.193779380888963e-08</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.085973100131748e-15</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.44279209514962e-14</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4.625730355422399e-08</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.15255363429082e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.396863820398997e-11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.204704950361928e-13</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.075920995233273e-08</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.291298379719497e-07</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.049540984365992e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.087160790437112e-14</v>
       </c>
     </row>
     <row r="15">
@@ -1237,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.372274245572353</v>
+        <v>2.372274485813316</v>
       </c>
       <c r="C15" t="n">
-        <v>246.864046</v>
+        <v>246.864071</v>
       </c>
       <c r="D15" t="n">
-        <v>24676.98287258192</v>
+        <v>24676.98537162779</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1659719054054712</v>
+        <v>0.1659719222134986</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4018106094184364</v>
+        <v>0.401810650109924</v>
       </c>
       <c r="G15" t="n">
-        <v>3.619950186854429</v>
+        <v>3.61995055344793</v>
       </c>
       <c r="H15" t="n">
-        <v>1.137663884539125e-06</v>
+        <v>1.137663999750706e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>1.836945102293684e-05</v>
+        <v>1.836945288321695e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>20.47272267724187</v>
+        <v>20.47272475052097</v>
       </c>
       <c r="K15" t="n">
-        <v>5942.874622691641</v>
+        <v>5942.875224528434</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0479478962161477</v>
+        <v>0.04794790107184631</v>
       </c>
       <c r="M15" t="n">
-        <v>2.20732996163157e-05</v>
+        <v>2.207330185168573e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.184409041405138</v>
+        <v>1.184409161350616</v>
       </c>
       <c r="O15" t="n">
-        <v>314.0121837730456</v>
+        <v>314.0122155731588</v>
       </c>
       <c r="P15" t="n">
-        <v>2908.719311240397</v>
+        <v>2908.719605807321</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.971430200279038e-05</v>
+        <v>1.971430399926398e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1292,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.93460500207599e-08</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002025715275123107</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.363780432545565e-09</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3.271823523976704e-09</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.945551855770619e-08</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8.644836186255819e-15</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.496549178351499e-13</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.665296943599801e-07</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.82127632773715e-05</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.950050936741946e-10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.795572225860633e-13</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>9.618706756615979e-09</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.571687364322876e-06</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.356844349081602e-05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.603285008943049e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1347,52 +1347,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.535842510735615e-07</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>6e-06</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002024651258799383</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.921061769562398e-09</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.61207603301822e-08</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.994391589752202e-07</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.735303522325891e-14</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4.275710758744828e-13</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5.701197946273908e-07</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001306764724934962</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.123231928096607e-09</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8.308122819448615e-13</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.373596260344379e-08</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>7.183841470481412e-06</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7.562517692529242e-05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.977126526235489e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1402,52 +1402,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.679212553678075e-08</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3e-06</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001012325629399692</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2.460530884781199e-09</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>8.060380165091098e-09</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.971957948761011e-08</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.367651761162945e-14</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.137855379372414e-13</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.850598973136954e-07</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>6.533823624674812e-05</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5.616159640483034e-10</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.154061409724307e-13</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.686798130172189e-08</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.591920735240706e-06</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.781258846264621e-05</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.488563263117744e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1457,52 +1457,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.970121042369717e-08</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002093206925936965</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.430732572169396e-09</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.297333115606302e-09</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.980478319598006e-08</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.666645512027277e-15</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.538320620500453e-13</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.711510459353892e-07</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.806812514006328e-05</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4.094938577137908e-10</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.809726022289982e-13</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.695297787985163e-09</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.585818833378694e-06</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36518113875655e-05</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.635190432742312e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1512,52 +1512,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.10348491597919</v>
+        <v>32.10349186988494</v>
       </c>
       <c r="C20" t="n">
-        <v>2866.916068</v>
+        <v>2866.916689000001</v>
       </c>
       <c r="D20" t="n">
-        <v>306830.2121997928</v>
+        <v>306830.2786619972</v>
       </c>
       <c r="E20" t="n">
-        <v>2.427835835619748</v>
+        <v>2.42783636151099</v>
       </c>
       <c r="F20" t="n">
-        <v>4.610650742030145</v>
+        <v>4.610651740738878</v>
       </c>
       <c r="G20" t="n">
-        <v>42.00067084146463</v>
+        <v>42.00067993919055</v>
       </c>
       <c r="H20" t="n">
-        <v>1.590207974861278e-05</v>
+        <v>1.590208319314736e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0003159216669163584</v>
+        <v>0.0003159217353478543</v>
       </c>
       <c r="J20" t="n">
-        <v>374.8685098001407</v>
+        <v>374.8685910000569</v>
       </c>
       <c r="K20" t="n">
-        <v>33256.65026775477</v>
+        <v>33256.65747144659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7686923875902628</v>
+        <v>0.7686925540959998</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0003677194992506845</v>
+        <v>0.0003677195789020603</v>
       </c>
       <c r="N20" t="n">
-        <v>14.98712483329792</v>
+        <v>14.98712807964497</v>
       </c>
       <c r="O20" t="n">
-        <v>3458.650855790516</v>
+        <v>3458.651604965634</v>
       </c>
       <c r="P20" t="n">
-        <v>36202.60447926377</v>
+        <v>36202.61232107597</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0003011229472339153</v>
+        <v>0.0003011230124598745</v>
       </c>
     </row>
     <row r="21">
@@ -1567,52 +1567,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.522097155880249e-08</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001676933150596182</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.14134352487837e-09</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.689305050829282e-09</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.444720519611344e-08</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8.365890642036602e-15</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.217670014523959e-13</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.741421146002726e-07</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.741419829771686e-05</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3.088927601268767e-10</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.270314029366631e-13</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.034927261237706e-08</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26910560663053e-06</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.347244349610564e-05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.615828231097389e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1622,52 +1622,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.363984741297122e-08</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001158754819792135</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.595739778297596e-09</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>7.739430553515355e-09</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.078064351972573e-07</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8.401737875428091e-15</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>9.395238048459947e-14</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.08573231727766e-07</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2.525401193922413e-05</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.361316813500573e-10</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.867401859638226e-13</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.730888526929076e-08</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.40755087578813e-06</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.756681371245885e-05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.912945747658015e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1732,52 +1732,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.597867997191271e-08</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001793015510597025</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.284732173145569e-09</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.795349597189015e-09</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.512220737250482e-08</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8.484905970912162e-15</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.341318220296551e-13</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.832260552545168e-07</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.815392814023804e-05</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3.633503280815465e-10</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.275510746652022e-13</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.044942645914631e-08</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.316323076813558e-06</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.346890584624323e-05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.663501354259483e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1787,52 +1787,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.26890005025324e-08</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3e-06</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002495214985404352</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.720607054245284e-09</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.035141403348695e-09</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.658625944309939e-08</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.25629095303583e-14</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1.828712240096704e-13</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.620660612740643e-07</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2.618997190837173e-05</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>4.681495279167999e-10</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.407048368337506e-13</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.551470191009377e-08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.908502586075638e-06</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.524003060356856e-05</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.421449657619455e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1842,52 +1842,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.260096078797602e-08</v>
+        <v>7.533653595992004e-09</v>
       </c>
       <c r="C26" t="n">
-        <v>3e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0002476341555375719</v>
+        <v>8.254471851252396e-05</v>
       </c>
       <c r="E26" t="n">
-        <v>1.700092172214484e-09</v>
+        <v>5.666973907381612e-10</v>
       </c>
       <c r="F26" t="n">
-        <v>4.030570761472976e-09</v>
+        <v>1.343523587157658e-09</v>
       </c>
       <c r="G26" t="n">
-        <v>3.658366025940175e-08</v>
+        <v>1.219455341980058e-08</v>
       </c>
       <c r="H26" t="n">
-        <v>1.526357347130652e-14</v>
+        <v>5.087857823768838e-15</v>
       </c>
       <c r="I26" t="n">
-        <v>1.819287879776797e-13</v>
+        <v>6.064292932589324e-14</v>
       </c>
       <c r="J26" t="n">
-        <v>2.658604161704019e-07</v>
+        <v>8.862013872346728e-08</v>
       </c>
       <c r="K26" t="n">
-        <v>2.654719942868352e-05</v>
+        <v>8.849066476227839e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>4.61365570398245e-10</v>
+        <v>1.537885234660816e-10</v>
       </c>
       <c r="M26" t="n">
-        <v>3.417814966883906e-13</v>
+        <v>1.139271655627969e-13</v>
       </c>
       <c r="N26" t="n">
-        <v>1.540331508056064e-08</v>
+        <v>5.13443836018688e-09</v>
       </c>
       <c r="O26" t="n">
-        <v>1.898598030438071e-06</v>
+        <v>6.328660101460234e-07</v>
       </c>
       <c r="P26" t="n">
-        <v>3.457577622068306e-05</v>
+        <v>1.152525874022768e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.438944910845363e-13</v>
+        <v>8.129816369484542e-14</v>
       </c>
     </row>
     <row r="27">
@@ -1897,52 +1897,52 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.913942203173305e-06</v>
+        <v>1.488758614308694e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>0.000958</v>
+        <v>0.00016</v>
       </c>
       <c r="D27" t="n">
-        <v>0.09476187820518459</v>
+        <v>0.01582661848938365</v>
       </c>
       <c r="E27" t="n">
-        <v>7.012138358087094e-07</v>
+        <v>1.171129579638763e-07</v>
       </c>
       <c r="F27" t="n">
-        <v>1.441501799214127e-06</v>
+        <v>2.407518662570567e-07</v>
       </c>
       <c r="G27" t="n">
-        <v>1.285596553791889e-05</v>
+        <v>2.147134119067874e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>4.463837241603917e-12</v>
+        <v>7.455260528774807e-13</v>
       </c>
       <c r="I27" t="n">
-        <v>8.014017298363966e-11</v>
+        <v>1.338458003902124e-11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0001003747004985497</v>
+        <v>1.676404183691852e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0.009654235988878686</v>
+        <v>0.001612398495011054</v>
       </c>
       <c r="L27" t="n">
-        <v>2.07911928693421e-07</v>
+        <v>3.472433047071749e-08</v>
       </c>
       <c r="M27" t="n">
-        <v>1.128404824006694e-10</v>
+        <v>1.884600958675062e-11</v>
       </c>
       <c r="N27" t="n">
-        <v>5.00093799738082e-06</v>
+        <v>8.352297281638113e-07</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0007964845744425104</v>
+        <v>0.0001330245635812126</v>
       </c>
       <c r="P27" t="n">
-        <v>0.01155007065624509</v>
+        <v>0.001929030589769535</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.675969807762335e-11</v>
+        <v>1.449013746599137e-11</v>
       </c>
     </row>
     <row r="28">
@@ -1952,52 +1952,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.812986537075435e-07</v>
+        <v>3.296339158318971e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000737985257453713</v>
+        <v>0.0001341791377188569</v>
       </c>
       <c r="E28" t="n">
-        <v>5.47302456051151e-09</v>
+        <v>9.950953746384561e-10</v>
       </c>
       <c r="F28" t="n">
-        <v>2.63057370265724e-08</v>
+        <v>4.782861277558617e-09</v>
       </c>
       <c r="G28" t="n">
-        <v>2.7984851717966e-07</v>
+        <v>5.088154857811998e-08</v>
       </c>
       <c r="H28" t="n">
-        <v>9.062612709741993e-14</v>
+        <v>1.647747765407634e-14</v>
       </c>
       <c r="I28" t="n">
-        <v>1.419249217226547e-12</v>
+        <v>2.580453122230085e-13</v>
       </c>
       <c r="J28" t="n">
-        <v>7.722097056182937e-07</v>
+        <v>1.404017646578715e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0001839002512793211</v>
+        <v>3.343640932351292e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>2.244632548736582e-09</v>
+        <v>4.081150088611965e-10</v>
       </c>
       <c r="M28" t="n">
-        <v>2.089279011455329e-12</v>
+        <v>3.79868911173696e-13</v>
       </c>
       <c r="N28" t="n">
-        <v>8.870683089249333e-08</v>
+        <v>1.612851470772606e-08</v>
       </c>
       <c r="O28" t="n">
-        <v>5.286206120789069e-06</v>
+        <v>9.611283855980124e-07</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0001505705837527228</v>
+        <v>2.737646977322232e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.551425586623679e-12</v>
+        <v>2.820773793861233e-13</v>
       </c>
     </row>
     <row r="29">
@@ -2007,52 +2007,52 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8.240847895797432e-08</v>
+        <v>1.648169579159486e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>5.000000000000001e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0003354478442971425</v>
+        <v>6.70895688594285e-05</v>
       </c>
       <c r="E29" t="n">
-        <v>2.487738436596142e-09</v>
+        <v>4.975476873192284e-10</v>
       </c>
       <c r="F29" t="n">
-        <v>1.195715319389654e-08</v>
+        <v>2.391430638779307e-09</v>
       </c>
       <c r="G29" t="n">
-        <v>1.272038714453e-07</v>
+        <v>2.544077428905999e-08</v>
       </c>
       <c r="H29" t="n">
-        <v>4.119369413519445e-14</v>
+        <v>8.238738827038887e-15</v>
       </c>
       <c r="I29" t="n">
-        <v>6.45113280557936e-13</v>
+        <v>1.290226561115872e-13</v>
       </c>
       <c r="J29" t="n">
-        <v>3.510044116446788e-07</v>
+        <v>7.020088232893575e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>8.359102330878233e-05</v>
+        <v>1.671820466175646e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>1.020287522152994e-09</v>
+        <v>2.040575044305988e-10</v>
       </c>
       <c r="M29" t="n">
-        <v>9.496722779342411e-13</v>
+        <v>1.899344555868482e-13</v>
       </c>
       <c r="N29" t="n">
-        <v>4.032128676931513e-08</v>
+        <v>8.064257353863023e-09</v>
       </c>
       <c r="O29" t="n">
-        <v>2.402820963995025e-06</v>
+        <v>4.805641927990049e-07</v>
       </c>
       <c r="P29" t="n">
-        <v>6.844117443305577e-05</v>
+        <v>1.368823488661115e-05</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.051934484653087e-13</v>
+        <v>1.410386896930617e-13</v>
       </c>
     </row>
     <row r="30">
@@ -2062,52 +2062,52 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.659519885017974e-06</v>
+        <v>5.477867603353309e-07</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000481</v>
+        <v>7.2e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01232781080317792</v>
+        <v>0.001845327188833285</v>
       </c>
       <c r="E30" t="n">
-        <v>6.387656350172681e-08</v>
+        <v>9.561564599011082e-09</v>
       </c>
       <c r="F30" t="n">
-        <v>1.025610718820542e-06</v>
+        <v>1.535217708005801e-07</v>
       </c>
       <c r="G30" t="n">
-        <v>1.255660621795539e-05</v>
+        <v>1.879575151128457e-06</v>
       </c>
       <c r="H30" t="n">
-        <v>4.861580498616873e-13</v>
+        <v>7.277209893979518e-14</v>
       </c>
       <c r="I30" t="n">
-        <v>5.804930131748792e-12</v>
+        <v>8.689292504904637e-13</v>
       </c>
       <c r="J30" t="n">
-        <v>5.251303462112981e-05</v>
+        <v>7.860578986946666e-06</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00191757872994748</v>
+        <v>0.0002870388119671904</v>
       </c>
       <c r="L30" t="n">
-        <v>7.649718251378549e-09</v>
+        <v>1.145072170684523e-09</v>
       </c>
       <c r="M30" t="n">
-        <v>2.69376523636063e-11</v>
+        <v>4.032247339250839e-12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.122816721964056e-06</v>
+        <v>3.177605072378628e-07</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0002600165836841555</v>
+        <v>3.892140129991518e-05</v>
       </c>
       <c r="P30" t="n">
-        <v>0.008742925175298184</v>
+        <v>0.001308712292352327</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.873129498052069e-11</v>
+        <v>7.29449737754156e-12</v>
       </c>
     </row>
     <row r="31">
@@ -2227,52 +2227,52 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.163327355642544e-07</v>
+        <v>2.704159194553179e-08</v>
       </c>
       <c r="C33" t="n">
-        <v>1.6e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001934114947859494</v>
+        <v>0.0002417643684824368</v>
       </c>
       <c r="E33" t="n">
-        <v>1.082036897947727e-08</v>
+        <v>1.352546122434659e-09</v>
       </c>
       <c r="F33" t="n">
-        <v>1.771620103026159e-07</v>
+        <v>2.214525128782699e-08</v>
       </c>
       <c r="G33" t="n">
-        <v>2.913714362267837e-07</v>
+        <v>3.642142952834796e-08</v>
       </c>
       <c r="H33" t="n">
-        <v>1.603170624641359e-13</v>
+        <v>2.003963280801699e-14</v>
       </c>
       <c r="I33" t="n">
-        <v>1.520477924079779e-12</v>
+        <v>1.900597405099723e-13</v>
       </c>
       <c r="J33" t="n">
-        <v>4.576842990394577e-06</v>
+        <v>5.721053737993221e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003392835227752361</v>
+        <v>4.241044034690452e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>2.219065621009561e-09</v>
+        <v>2.773832026261952e-10</v>
       </c>
       <c r="M33" t="n">
-        <v>1.989137607258483e-12</v>
+        <v>2.486422009073103e-13</v>
       </c>
       <c r="N33" t="n">
-        <v>9.650372937073417e-08</v>
+        <v>1.206296617134177e-08</v>
       </c>
       <c r="O33" t="n">
-        <v>1.503369242750021e-05</v>
+        <v>1.879211553437526e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0002047503600051375</v>
+        <v>2.559379500064218e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.619195596434243e-12</v>
+        <v>2.023994495542804e-13</v>
       </c>
     </row>
     <row r="34">
@@ -2282,52 +2282,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.757703476459567e-07</v>
+        <v>2.704159194553179e-08</v>
       </c>
       <c r="C34" t="n">
-        <v>1.3e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001571468395135839</v>
+        <v>0.0002417643684824368</v>
       </c>
       <c r="E34" t="n">
-        <v>8.791549795825285e-09</v>
+        <v>1.352546122434659e-09</v>
       </c>
       <c r="F34" t="n">
-        <v>1.439441333708754e-07</v>
+        <v>2.214525128782699e-08</v>
       </c>
       <c r="G34" t="n">
-        <v>2.367392919342618e-07</v>
+        <v>3.642142952834796e-08</v>
       </c>
       <c r="H34" t="n">
-        <v>1.302576132521105e-13</v>
+        <v>2.003963280801699e-14</v>
       </c>
       <c r="I34" t="n">
-        <v>1.23538831331482e-12</v>
+        <v>1.900597405099723e-13</v>
       </c>
       <c r="J34" t="n">
-        <v>3.718684929695594e-06</v>
+        <v>5.721053737993221e-07</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0002756678622548794</v>
+        <v>4.241044034690452e-05</v>
       </c>
       <c r="L34" t="n">
-        <v>1.802990817070268e-09</v>
+        <v>2.773832026261952e-10</v>
       </c>
       <c r="M34" t="n">
-        <v>1.616174305897517e-12</v>
+        <v>2.486422009073103e-13</v>
       </c>
       <c r="N34" t="n">
-        <v>7.840928011372151e-08</v>
+        <v>1.206296617134177e-08</v>
       </c>
       <c r="O34" t="n">
-        <v>1.221487509734392e-05</v>
+        <v>1.879211553437526e-06</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0001663596675041742</v>
+        <v>2.559379500064218e-05</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.315596422102823e-12</v>
+        <v>2.023994495542804e-13</v>
       </c>
     </row>
     <row r="35">
@@ -2337,52 +2337,52 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.477615641140676e-07</v>
+        <v>3.283590313645946e-08</v>
       </c>
       <c r="C35" t="n">
-        <v>9e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>0.001293009768140713</v>
+        <v>0.0002873355040312695</v>
       </c>
       <c r="E35" t="n">
-        <v>1.11518850409316e-08</v>
+        <v>2.478196675762578e-09</v>
       </c>
       <c r="F35" t="n">
-        <v>1.552589033423493e-08</v>
+        <v>3.450197852052206e-09</v>
       </c>
       <c r="G35" t="n">
-        <v>1.561433326636267e-07</v>
+        <v>3.469851836969482e-08</v>
       </c>
       <c r="H35" t="n">
-        <v>1.042986593109744e-13</v>
+        <v>2.317747984688321e-14</v>
       </c>
       <c r="I35" t="n">
-        <v>1.801835744209399e-12</v>
+        <v>4.004079431576442e-13</v>
       </c>
       <c r="J35" t="n">
-        <v>7.733041612803625e-07</v>
+        <v>1.718453691734139e-07</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0001148928377358675</v>
+        <v>2.553174171908167e-05</v>
       </c>
       <c r="L35" t="n">
-        <v>2.744274552794375e-09</v>
+        <v>6.098387895098611e-10</v>
       </c>
       <c r="M35" t="n">
-        <v>1.173991761509017e-12</v>
+        <v>2.608870581131148e-13</v>
       </c>
       <c r="N35" t="n">
-        <v>5.453854285186774e-08</v>
+        <v>1.211967618930394e-08</v>
       </c>
       <c r="O35" t="n">
-        <v>7.244663850735338e-06</v>
+        <v>1.609925300163408e-06</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0001073231154764802</v>
+        <v>2.384958121699559e-05</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.46673822076585e-13</v>
+        <v>1.437052937947967e-13</v>
       </c>
     </row>
     <row r="36">
@@ -2392,52 +2392,52 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.313436125458378e-07</v>
+        <v>1.641795156822973e-08</v>
       </c>
       <c r="C36" t="n">
-        <v>8e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>0.001149342016125078</v>
+        <v>0.0001436677520156348</v>
       </c>
       <c r="E36" t="n">
-        <v>9.912786703050312e-09</v>
+        <v>1.239098337881289e-09</v>
       </c>
       <c r="F36" t="n">
-        <v>1.380079140820882e-08</v>
+        <v>1.725098926026103e-09</v>
       </c>
       <c r="G36" t="n">
-        <v>1.387940734787793e-07</v>
+        <v>1.734925918484741e-08</v>
       </c>
       <c r="H36" t="n">
-        <v>9.270991938753283e-14</v>
+        <v>1.15887399234416e-14</v>
       </c>
       <c r="I36" t="n">
-        <v>1.601631772630577e-12</v>
+        <v>2.002039715788221e-13</v>
       </c>
       <c r="J36" t="n">
-        <v>6.873814766936555e-07</v>
+        <v>8.592268458670694e-08</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0001021269668763267</v>
+        <v>1.276587085954083e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>2.439355158039444e-09</v>
+        <v>3.049193947549305e-10</v>
       </c>
       <c r="M36" t="n">
-        <v>1.043548232452459e-12</v>
+        <v>1.304435290565574e-13</v>
       </c>
       <c r="N36" t="n">
-        <v>4.847870475721576e-08</v>
+        <v>6.05983809465197e-09</v>
       </c>
       <c r="O36" t="n">
-        <v>6.439701200653634e-06</v>
+        <v>8.049626500817042e-07</v>
       </c>
       <c r="P36" t="n">
-        <v>9.539832486798237e-05</v>
+        <v>1.19247906084978e-05</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.748211751791866e-13</v>
+        <v>7.185264689739833e-14</v>
       </c>
     </row>
     <row r="37">
@@ -2447,52 +2447,52 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.051606040725022e-07</v>
+        <v>2.003059125190518e-08</v>
       </c>
       <c r="C37" t="n">
-        <v>2.1e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0006013554095439039</v>
+        <v>0.0001145438875321721</v>
       </c>
       <c r="E37" t="n">
-        <v>3.421048144398913e-09</v>
+        <v>6.516282179807453e-10</v>
       </c>
       <c r="F37" t="n">
-        <v>3.310441728369961e-08</v>
+        <v>6.305603292133257e-09</v>
       </c>
       <c r="G37" t="n">
-        <v>3.188992846437693e-07</v>
+        <v>6.074272088452746e-08</v>
       </c>
       <c r="H37" t="n">
-        <v>3.119890571126569e-14</v>
+        <v>5.942648706907748e-15</v>
       </c>
       <c r="I37" t="n">
-        <v>5.741969636840167e-13</v>
+        <v>1.09370850225527e-13</v>
       </c>
       <c r="J37" t="n">
-        <v>1.040337703832529e-06</v>
+        <v>1.981595626347673e-07</v>
       </c>
       <c r="K37" t="n">
-        <v>0.001155202194183269</v>
+        <v>0.0002200385131777654</v>
       </c>
       <c r="L37" t="n">
-        <v>5.143200614737926e-10</v>
+        <v>9.796572599500808e-11</v>
       </c>
       <c r="M37" t="n">
-        <v>2.06017571921077e-12</v>
+        <v>3.924144227068133e-13</v>
       </c>
       <c r="N37" t="n">
-        <v>8.389295492968282e-08</v>
+        <v>1.597961046279672e-08</v>
       </c>
       <c r="O37" t="n">
-        <v>8.362877468977983e-06</v>
+        <v>1.592929041710092e-06</v>
       </c>
       <c r="P37" t="n">
-        <v>0.000170002083237794</v>
+        <v>3.238134918815123e-05</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.994495354906048e-12</v>
+        <v>3.799038771249615e-13</v>
       </c>
     </row>
     <row r="38">
@@ -2502,52 +2502,52 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.166409216784434e-07</v>
+        <v>3.466254746855093e-08</v>
       </c>
       <c r="C38" t="n">
-        <v>2.5e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001320965775944962</v>
+        <v>0.0002113545241511939</v>
       </c>
       <c r="E38" t="n">
-        <v>1.170140889471188e-08</v>
+        <v>1.8722254231539e-09</v>
       </c>
       <c r="F38" t="n">
-        <v>3.102115453067425e-08</v>
+        <v>4.963384724907879e-09</v>
       </c>
       <c r="G38" t="n">
-        <v>3.198003998958619e-07</v>
+        <v>5.11680639833379e-08</v>
       </c>
       <c r="H38" t="n">
-        <v>9.352595322163287e-14</v>
+        <v>1.496415251546126e-14</v>
       </c>
       <c r="I38" t="n">
-        <v>1.347623347652875e-12</v>
+        <v>2.156197356244599e-13</v>
       </c>
       <c r="J38" t="n">
-        <v>1.945408285087861e-06</v>
+        <v>3.112653256140577e-07</v>
       </c>
       <c r="K38" t="n">
-        <v>0.000199918983027565</v>
+        <v>3.19870372844104e-05</v>
       </c>
       <c r="L38" t="n">
-        <v>1.4392382106039e-09</v>
+        <v>2.30278113696624e-10</v>
       </c>
       <c r="M38" t="n">
-        <v>2.45948621839503e-12</v>
+        <v>3.935177949432047e-13</v>
       </c>
       <c r="N38" t="n">
-        <v>1.061530959080687e-07</v>
+        <v>1.698449534529098e-08</v>
       </c>
       <c r="O38" t="n">
-        <v>9.870048246952371e-06</v>
+        <v>1.579207719512379e-06</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0002905931002626261</v>
+        <v>4.649489604202017e-05</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.798005310066062e-12</v>
+        <v>2.876808496105699e-13</v>
       </c>
     </row>
     <row r="39">
@@ -2557,52 +2557,52 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.993096479441679e-07</v>
+        <v>3.466254746855093e-08</v>
       </c>
       <c r="C39" t="n">
-        <v>2.3e-05</v>
+        <v>4e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001215288513869365</v>
+        <v>0.0002113545241511939</v>
       </c>
       <c r="E39" t="n">
-        <v>1.076529618313492e-08</v>
+        <v>1.8722254231539e-09</v>
       </c>
       <c r="F39" t="n">
-        <v>2.85394621682203e-08</v>
+        <v>4.963384724907879e-09</v>
       </c>
       <c r="G39" t="n">
-        <v>2.94216367904193e-07</v>
+        <v>5.11680639833379e-08</v>
       </c>
       <c r="H39" t="n">
-        <v>8.604387696390222e-14</v>
+        <v>1.496415251546126e-14</v>
       </c>
       <c r="I39" t="n">
-        <v>1.239813479840645e-12</v>
+        <v>2.156197356244599e-13</v>
       </c>
       <c r="J39" t="n">
-        <v>1.789775622280832e-06</v>
+        <v>3.112653256140577e-07</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0001839254643853598</v>
+        <v>3.19870372844104e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>1.324099153755588e-09</v>
+        <v>2.30278113696624e-10</v>
       </c>
       <c r="M39" t="n">
-        <v>2.262727320923427e-12</v>
+        <v>3.935177949432047e-13</v>
       </c>
       <c r="N39" t="n">
-        <v>9.766084823542315e-08</v>
+        <v>1.698449534529098e-08</v>
       </c>
       <c r="O39" t="n">
-        <v>9.080444387196181e-06</v>
+        <v>1.579207719512379e-06</v>
       </c>
       <c r="P39" t="n">
-        <v>0.000267345652241616</v>
+        <v>4.649489604202017e-05</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.654164885260777e-12</v>
+        <v>2.876808496105699e-13</v>
       </c>
     </row>
     <row r="40">
@@ -2612,52 +2612,52 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.474425719042268e-08</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001206857945686773</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7.898547181569792e-10</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.162451174138798e-09</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2.407523185544934e-08</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>5.907230470442138e-14</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1.75765337446112e-13</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2.06251463185342e-07</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.50333682431695e-05</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.904672029778269e-10</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.275738172951511e-13</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>7.93240432346108e-09</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.031915826878937e-06</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.006689315542802e-05</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.180749423926056e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2667,52 +2667,52 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.24413625014887</v>
+        <v>1.223062925256141</v>
       </c>
       <c r="C41" t="n">
-        <v>114.90516</v>
+        <v>112.958883</v>
       </c>
       <c r="D41" t="n">
-        <v>11124.79637576965</v>
+        <v>10936.36327741407</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09530046116008407</v>
+        <v>0.09368625083528</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07432435803136615</v>
+        <v>0.07306544338753107</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9199804263391161</v>
+        <v>0.9043976905922271</v>
       </c>
       <c r="H41" t="n">
-        <v>3.456478923831088e-07</v>
+        <v>3.397932680734283e-07</v>
       </c>
       <c r="I41" t="n">
-        <v>1.65225544688123e-05</v>
+        <v>1.624269351440523e-05</v>
       </c>
       <c r="J41" t="n">
-        <v>3.481984169791736</v>
+        <v>3.423005915864499</v>
       </c>
       <c r="K41" t="n">
-        <v>594.0201087021796</v>
+        <v>583.95852682801</v>
       </c>
       <c r="L41" t="n">
-        <v>0.02901832207192857</v>
+        <v>0.02852680634863828</v>
       </c>
       <c r="M41" t="n">
-        <v>4.875509760597425e-06</v>
+        <v>4.792927807704045e-06</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2993756091565044</v>
+        <v>0.2943047501762611</v>
       </c>
       <c r="O41" t="n">
-        <v>28.79306747374146</v>
+        <v>28.30536713910382</v>
       </c>
       <c r="P41" t="n">
-        <v>414.9461482677639</v>
+        <v>407.9177420185394</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.000237315814611496</v>
+        <v>0.0002332961316684966</v>
       </c>
     </row>
     <row r="42">
@@ -2722,52 +2722,52 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.734523231160349e-05</v>
+        <v>3.213897359009983e-06</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0007070000000000001</v>
+        <v>0.000131</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1422360680533915</v>
+        <v>0.02635491501413618</v>
       </c>
       <c r="E42" t="n">
-        <v>1.184380746467125e-06</v>
+        <v>2.194538582562848e-07</v>
       </c>
       <c r="F42" t="n">
-        <v>1.271531609043438e-06</v>
+        <v>2.356020378849935e-07</v>
       </c>
       <c r="G42" t="n">
-        <v>1.517196579506096e-05</v>
+        <v>2.811212898377633e-06</v>
       </c>
       <c r="H42" t="n">
-        <v>7.151871847275938e-12</v>
+        <v>1.325170031107706e-12</v>
       </c>
       <c r="I42" t="n">
-        <v>1.981729328435674e-10</v>
+        <v>3.671945431754927e-11</v>
       </c>
       <c r="J42" t="n">
-        <v>5.143869181507388e-05</v>
+        <v>9.531073023726562e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.009987611561629445</v>
+        <v>0.001850604122451849</v>
       </c>
       <c r="L42" t="n">
-        <v>3.45808915097927e-07</v>
+        <v>6.407491920484929e-08</v>
       </c>
       <c r="M42" t="n">
-        <v>8.953799714115106e-11</v>
+        <v>1.659049169093464e-11</v>
       </c>
       <c r="N42" t="n">
-        <v>4.421624157908704e-06</v>
+        <v>8.192825525969453e-07</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0004476066032493803</v>
+        <v>8.293700852286963e-05</v>
       </c>
       <c r="P42" t="n">
-        <v>0.007871491382835589</v>
+        <v>0.001458508304316071</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.925533011763745e-11</v>
+        <v>1.09794176031266e-11</v>
       </c>
     </row>
     <row r="43">
@@ -2777,52 +2777,52 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5419110404698283</v>
+        <v>0.6003360267419147</v>
       </c>
       <c r="C43" t="n">
-        <v>39.25055399999999</v>
+        <v>43.482269</v>
       </c>
       <c r="D43" t="n">
-        <v>2823.664281646752</v>
+        <v>3128.091640700304</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02299188626240358</v>
+        <v>0.02547070757980224</v>
       </c>
       <c r="F43" t="n">
-        <v>0.07885290357176361</v>
+        <v>0.08735426166312167</v>
       </c>
       <c r="G43" t="n">
-        <v>1.557743974880438</v>
+        <v>1.725688828465465</v>
       </c>
       <c r="H43" t="n">
-        <v>2.763835226213874e-07</v>
+        <v>3.061812242902547e-07</v>
       </c>
       <c r="I43" t="n">
-        <v>2.955969547919805e-06</v>
+        <v>3.27466111786492e-06</v>
       </c>
       <c r="J43" t="n">
-        <v>3.061643287087939</v>
+        <v>3.391727846470702</v>
       </c>
       <c r="K43" t="n">
-        <v>424.4542577854469</v>
+        <v>470.2158908437866</v>
       </c>
       <c r="L43" t="n">
-        <v>0.005423467980912157</v>
+        <v>0.006008187646444667</v>
       </c>
       <c r="M43" t="n">
-        <v>6.789624759415578e-06</v>
+        <v>7.521633712430365e-06</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2467373409204133</v>
+        <v>0.2733388025617708</v>
       </c>
       <c r="O43" t="n">
-        <v>23.5747247920674</v>
+        <v>26.11638360593952</v>
       </c>
       <c r="P43" t="n">
-        <v>518.1486165250218</v>
+        <v>574.0117075982889</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.833426000261183e-06</v>
+        <v>4.246718671409094e-06</v>
       </c>
     </row>
     <row r="44">
@@ -2887,52 +2887,52 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4.84466158814699e-09</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>3.544158267331987e-05</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3.172474612851784e-10</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1.069838146953616e-09</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.067143711593992e-08</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.647213675570826e-14</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1.777884487069898e-13</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>6.803002645528529e-08</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7.454924969324359e-06</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.065840160446065e-11</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.193603930877381e-13</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.712065055457427e-09</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.313175820986644e-07</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.17420750794105e-05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.272424540452605e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2942,52 +2942,52 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.84466158814699e-09</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>3.544158267331987e-05</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3.172474612851784e-10</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>1.069838146953616e-09</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.067143711593992e-08</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.647213675570826e-14</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1.777884487069898e-13</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>6.803002645528529e-08</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>7.454924969324359e-06</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1.065840160446065e-11</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.193603930877381e-13</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.712065055457427e-09</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.313175820986644e-07</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.17420750794105e-05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.272424540452605e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2997,52 +2997,52 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4.621517262970278e-08</v>
+        <v>9.243034525940554e-09</v>
       </c>
       <c r="C47" t="n">
-        <v>5e-06</v>
+        <v>9.999999999999997e-07</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0002146767527198391</v>
+        <v>4.29353505439678e-05</v>
       </c>
       <c r="E47" t="n">
-        <v>1.890823377998581e-09</v>
+        <v>3.781646755997161e-10</v>
       </c>
       <c r="F47" t="n">
-        <v>8.372599305946247e-09</v>
+        <v>1.674519861189249e-09</v>
       </c>
       <c r="G47" t="n">
-        <v>7.356566974739063e-08</v>
+        <v>1.471313394947812e-08</v>
       </c>
       <c r="H47" t="n">
-        <v>4.614085789661953e-14</v>
+        <v>9.228171579323904e-15</v>
       </c>
       <c r="I47" t="n">
-        <v>2.823325847400379e-13</v>
+        <v>5.646651694800756e-14</v>
       </c>
       <c r="J47" t="n">
-        <v>3.866665561921007e-07</v>
+        <v>7.733331123842011e-08</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0001265235069779615</v>
+        <v>2.530470139559228e-05</v>
       </c>
       <c r="L47" t="n">
-        <v>1.519251875621012e-10</v>
+        <v>3.038503751242023e-11</v>
       </c>
       <c r="M47" t="n">
-        <v>6.359244680049618e-13</v>
+        <v>1.271848936009923e-13</v>
       </c>
       <c r="N47" t="n">
-        <v>2.804835414986092e-08</v>
+        <v>5.609670829972183e-09</v>
       </c>
       <c r="O47" t="n">
-        <v>4.279701068185913e-06</v>
+        <v>8.559402136371823e-07</v>
       </c>
       <c r="P47" t="n">
-        <v>6.115493762723675e-05</v>
+        <v>1.223098752544734e-05</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.685235101330409e-13</v>
+        <v>9.370470202660813e-14</v>
       </c>
     </row>
     <row r="48">
@@ -3052,52 +3052,52 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.241461703206709e-08</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.000126100361500976</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.047907393547254e-09</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>4.599135387906703e-09</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>4.803851313138683e-08</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.150263724120411e-14</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1.463692980501883e-13</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1.088657659109754e-07</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0001101903430093154</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2.016040966854539e-10</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.512739516447805e-13</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.442001325000888e-08</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>8.482360368789981e-07</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.262124402975133e-05</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.712217218509247e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3107,52 +3107,52 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2641404364478788</v>
+        <v>0.2093843368662981</v>
       </c>
       <c r="C49" t="n">
-        <v>16.02629</v>
+        <v>12.704053</v>
       </c>
       <c r="D49" t="n">
-        <v>1075.196886516169</v>
+        <v>852.3094385373283</v>
       </c>
       <c r="E49" t="n">
-        <v>0.007973843525807274</v>
+        <v>0.006320872189730905</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03832576093196243</v>
+        <v>0.03038086158087618</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4077212265810186</v>
+        <v>0.3232009449292549</v>
       </c>
       <c r="H49" t="n">
-        <v>1.320364176763751e-07</v>
+        <v>1.04665374711852e-07</v>
       </c>
       <c r="I49" t="n">
-        <v>2.067754503413395e-06</v>
+        <v>1.639110661441447e-06</v>
       </c>
       <c r="J49" t="n">
-        <v>1.1250596984594</v>
+        <v>0.8918357297535633</v>
       </c>
       <c r="K49" t="n">
-        <v>267.9307961886607</v>
+        <v>212.388958087801</v>
       </c>
       <c r="L49" t="n">
-        <v>0.003270284742681052</v>
+        <v>0.002592357351334055</v>
       </c>
       <c r="M49" t="n">
-        <v>3.043944666226947e-06</v>
+        <v>2.412937390301464e-06</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1292401269876414</v>
+        <v>0.1024487528291156</v>
       </c>
       <c r="O49" t="n">
-        <v>7.701661117412741</v>
+        <v>6.10511297522076</v>
       </c>
       <c r="P49" t="n">
-        <v>219.3716218809473</v>
+        <v>173.896061475957</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.260326942241019e-06</v>
+        <v>1.791762988911211e-06</v>
       </c>
     </row>
     <row r="50">
@@ -3162,52 +3162,52 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.594539813057172e-08</v>
+        <v>4.324233021761951e-09</v>
       </c>
       <c r="C50" t="n">
-        <v>6.000000000000001e-06</v>
+        <v>9.999999999999997e-07</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001618420248223232</v>
+        <v>2.697367080372052e-05</v>
       </c>
       <c r="E50" t="n">
-        <v>1.498346477842254e-09</v>
+        <v>2.497244129737088e-10</v>
       </c>
       <c r="F50" t="n">
-        <v>7.651326905143823e-09</v>
+        <v>1.275221150857303e-09</v>
       </c>
       <c r="G50" t="n">
-        <v>7.257764224273853e-08</v>
+        <v>1.209627370712308e-08</v>
       </c>
       <c r="H50" t="n">
-        <v>2.883484476151954e-14</v>
+        <v>4.805807460253255e-15</v>
       </c>
       <c r="I50" t="n">
-        <v>1.495303907155435e-13</v>
+        <v>2.492173178592391e-14</v>
       </c>
       <c r="J50" t="n">
-        <v>3.167044386273277e-07</v>
+        <v>5.278407310455459e-08</v>
       </c>
       <c r="K50" t="n">
-        <v>7.142244515087265e-05</v>
+        <v>1.190374085847877e-05</v>
       </c>
       <c r="L50" t="n">
-        <v>6.226483016854771e-11</v>
+        <v>1.037747169475795e-11</v>
       </c>
       <c r="M50" t="n">
-        <v>7.256426814779397e-13</v>
+        <v>1.209404469129899e-13</v>
       </c>
       <c r="N50" t="n">
-        <v>2.58082529864754e-08</v>
+        <v>4.301375497745899e-09</v>
       </c>
       <c r="O50" t="n">
-        <v>2.828907382107922e-06</v>
+        <v>4.714845636846535e-07</v>
       </c>
       <c r="P50" t="n">
-        <v>6.463748636002389e-05</v>
+        <v>1.077291439333731e-05</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.943470320887243e-13</v>
+        <v>1.157245053481207e-13</v>
       </c>
     </row>
     <row r="51">
@@ -3217,52 +3217,52 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.832648003582197e-07</v>
+        <v>6.844014292111066e-08</v>
       </c>
       <c r="C51" t="n">
-        <v>5.600000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>0.002636221334602543</v>
+        <v>0.000470753809750454</v>
       </c>
       <c r="E51" t="n">
-        <v>2.160650610167397e-08</v>
+        <v>3.858304661013209e-09</v>
       </c>
       <c r="F51" t="n">
-        <v>8.614450397077675e-08</v>
+        <v>1.538294713763871e-08</v>
       </c>
       <c r="G51" t="n">
-        <v>8.473454280896343e-07</v>
+        <v>1.513116835874347e-07</v>
       </c>
       <c r="H51" t="n">
-        <v>3.942064351617615e-13</v>
+        <v>7.039400627888598e-14</v>
       </c>
       <c r="I51" t="n">
-        <v>5.645677363117185e-12</v>
+        <v>1.008156671985212e-12</v>
       </c>
       <c r="J51" t="n">
-        <v>2.997082031888546e-06</v>
+        <v>5.351932199800975e-07</v>
       </c>
       <c r="K51" t="n">
-        <v>0.001785631827783473</v>
+        <v>0.0003188628263899059</v>
       </c>
       <c r="L51" t="n">
-        <v>3.25534186643157e-09</v>
+        <v>5.81311047577066e-10</v>
       </c>
       <c r="M51" t="n">
-        <v>9.007822328290581e-12</v>
+        <v>1.608539701480461e-12</v>
       </c>
       <c r="N51" t="n">
-        <v>2.766702668419091e-07</v>
+        <v>4.940540479319806e-08</v>
       </c>
       <c r="O51" t="n">
-        <v>2.487867781129655e-05</v>
+        <v>4.442621037731526e-06</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0005823874946928152</v>
+        <v>0.0001039977669094313</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.23206597059153e-12</v>
+        <v>9.342974947484875e-13</v>
       </c>
     </row>
     <row r="52">
@@ -3272,52 +3272,52 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.394860177790153e-08</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>8.792378254855287e-05</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>8.013701916271365e-10</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>3.009415329920938e-09</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.595816505300803e-08</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.635043965411827e-14</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1.161970978043199e-13</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1.538936608915078e-07</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>4.090933036008861e-05</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>6.590121712694782e-11</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.46220610800033e-13</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.046736507843763e-08</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1.650386821277994e-06</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.368909935177825e-05</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8.171402863890408e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3382,52 +3382,52 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2947547564555207</v>
+        <v>0.3210518655069903</v>
       </c>
       <c r="C54" t="n">
-        <v>27.222776</v>
+        <v>29.651508</v>
       </c>
       <c r="D54" t="n">
-        <v>2635.633071510357</v>
+        <v>2870.776114271151</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02257812535884088</v>
+        <v>0.0245924759731584</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01760856823167629</v>
+        <v>0.01917955030706991</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2179573229837046</v>
+        <v>0.2374028022017263</v>
       </c>
       <c r="H54" t="n">
-        <v>8.188923064218764e-08</v>
+        <v>8.919513489368873e-08</v>
       </c>
       <c r="I54" t="n">
-        <v>3.914443870512657e-06</v>
+        <v>4.263678463285927e-06</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8249348862121281</v>
+        <v>0.8985330290341443</v>
       </c>
       <c r="K54" t="n">
-        <v>140.7323775424453</v>
+        <v>153.2880856294317</v>
       </c>
       <c r="L54" t="n">
-        <v>0.006874880829198333</v>
+        <v>0.007488236464423064</v>
       </c>
       <c r="M54" t="n">
-        <v>1.15508224433574e-06</v>
+        <v>1.258135114823674e-06</v>
       </c>
       <c r="N54" t="n">
-        <v>0.07092662460007075</v>
+        <v>0.07725447899736584</v>
       </c>
       <c r="O54" t="n">
-        <v>6.821514596825324</v>
+        <v>7.430109061613807</v>
       </c>
       <c r="P54" t="n">
-        <v>98.30703900813612</v>
+        <v>107.0776894173489</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.622371756347827e-05</v>
+        <v>6.12398240033719e-05</v>
       </c>
     </row>
     <row r="55">
@@ -3437,52 +3437,52 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.717349733822128e-06</v>
+        <v>4.416042172685473e-07</v>
       </c>
       <c r="C55" t="n">
-        <v>6.999999999999998e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01408277901518727</v>
+        <v>0.003621286032476728</v>
       </c>
       <c r="E55" t="n">
-        <v>1.172654204422895e-07</v>
+        <v>3.015396525658875e-08</v>
       </c>
       <c r="F55" t="n">
-        <v>1.25894218717172e-07</v>
+        <v>3.23727990987014e-08</v>
       </c>
       <c r="G55" t="n">
-        <v>1.502174831194154e-06</v>
+        <v>3.862735280213542e-07</v>
       </c>
       <c r="H55" t="n">
-        <v>7.08106123492667e-13</v>
+        <v>1.820844317552573e-13</v>
       </c>
       <c r="I55" t="n">
-        <v>1.962108245975914e-11</v>
+        <v>5.045421203938067e-12</v>
       </c>
       <c r="J55" t="n">
-        <v>5.092939783670681e-06</v>
+        <v>1.309613087229604e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0009888724318444992</v>
+        <v>0.0002542814824742999</v>
       </c>
       <c r="L55" t="n">
-        <v>3.42385064453393e-08</v>
+        <v>8.804187371658682e-09</v>
       </c>
       <c r="M55" t="n">
-        <v>8.865148231797133e-12</v>
+        <v>2.279609545319264e-12</v>
       </c>
       <c r="N55" t="n">
-        <v>4.377845700899706e-07</v>
+        <v>1.125731751659925e-07</v>
       </c>
       <c r="O55" t="n">
-        <v>4.431748547023566e-05</v>
+        <v>1.139592483520346e-05</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0007793555824589691</v>
+        <v>0.000200405721203735</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.866864368082915e-12</v>
+        <v>1.508622266078464e-12</v>
       </c>
     </row>
     <row r="56">
@@ -3492,52 +3492,52 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5.308879107604057e-05</v>
+        <v>1.121868182755091e-05</v>
       </c>
       <c r="C56" t="n">
-        <v>0.002455999999999999</v>
+        <v>0.0005189999999999993</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4774810757945087</v>
+        <v>0.1009009276617874</v>
       </c>
       <c r="E56" t="n">
-        <v>4.25493016127633e-06</v>
+        <v>8.991485153511456e-07</v>
       </c>
       <c r="F56" t="n">
-        <v>5.285177815421281e-06</v>
+        <v>1.116859644219724e-06</v>
       </c>
       <c r="G56" t="n">
-        <v>5.269977626997307e-05</v>
+        <v>1.113647552284853e-05</v>
       </c>
       <c r="H56" t="n">
-        <v>3.449203277458406e-11</v>
+        <v>7.288829401469507e-12</v>
       </c>
       <c r="I56" t="n">
-        <v>7.201500842344913e-10</v>
+        <v>1.521815528166533e-10</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0001945491654011647</v>
+        <v>4.111197754202134e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.03953741087609733</v>
+        <v>0.008355014757611764</v>
       </c>
       <c r="L56" t="n">
-        <v>1.0883191079852e-06</v>
+        <v>2.299827430962207e-07</v>
       </c>
       <c r="M56" t="n">
-        <v>3.714811171303076e-10</v>
+        <v>7.85010992632856e-11</v>
       </c>
       <c r="N56" t="n">
-        <v>1.883075053497249e-05</v>
+        <v>3.979299481942472e-06</v>
       </c>
       <c r="O56" t="n">
-        <v>0.002526880105293674</v>
+        <v>0.0005339783284395015</v>
       </c>
       <c r="P56" t="n">
-        <v>0.02853111325530274</v>
+        <v>0.006029172548657209</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.933975684029662e-10</v>
+        <v>4.086862296463328e-11</v>
       </c>
     </row>
     <row r="57">
@@ -3602,52 +3602,52 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9.590852691522149e-09</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>9.999999999999997e-07</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>5.018056459904523e-05</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>4.075757441474988e-10</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2.333580463487034e-09</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.385681391027146e-08</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3.558751348905606e-15</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>5.82896189792841e-14</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>5.448136273373896e-08</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00012738871398696</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>6.581477682751649e-11</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.849447727463358e-13</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6.994114593794953e-09</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.965943469781058e-07</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.028424400729848e-05</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9.169179363329502e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3657,52 +3657,52 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5.801722933554263e-05</v>
+        <v>0.004469898957752929</v>
       </c>
       <c r="C59" t="n">
-        <v>0.002683999999999998</v>
+        <v>0.206787</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5218074948829241</v>
+        <v>40.20231238612343</v>
       </c>
       <c r="E59" t="n">
-        <v>4.64993182119938e-06</v>
+        <v>0.0003582509133794176</v>
       </c>
       <c r="F59" t="n">
-        <v>5.775821358546712e-06</v>
+        <v>0.0004449943261064828</v>
       </c>
       <c r="G59" t="n">
-        <v>5.759210077712045e-05</v>
+        <v>0.00443714520990999</v>
       </c>
       <c r="H59" t="n">
-        <v>3.769406187580754e-11</v>
+        <v>2.904113998924225e-09</v>
       </c>
       <c r="I59" t="n">
-        <v>7.870044080152091e-10</v>
+        <v>6.063423268265319e-08</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0002126099185410124</v>
+        <v>0.01638039017337569</v>
       </c>
       <c r="K59" t="n">
-        <v>0.04320782198348747</v>
+        <v>3.328917989753886</v>
       </c>
       <c r="L59" t="n">
-        <v>1.189351989345389e-06</v>
+        <v>9.163283525363827e-05</v>
       </c>
       <c r="M59" t="n">
-        <v>4.059671491766066e-10</v>
+        <v>3.127746977525447e-08</v>
       </c>
       <c r="N59" t="n">
-        <v>2.057888209929404e-05</v>
+        <v>0.001585486323646319</v>
       </c>
       <c r="O59" t="n">
-        <v>0.002761460180215075</v>
+        <v>0.2127548682139102</v>
       </c>
       <c r="P59" t="n">
-        <v>0.03117976709170709</v>
+        <v>2.402224477493606</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.113514143296258e-10</v>
+        <v>1.62834295510359e-08</v>
       </c>
     </row>
     <row r="60">
@@ -3712,52 +3712,52 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.109564361365079</v>
+        <v>3.883282643503202</v>
       </c>
       <c r="C60" t="n">
-        <v>540.152949</v>
+        <v>510.4109309999999</v>
       </c>
       <c r="D60" t="n">
-        <v>13843.87392941913</v>
+        <v>13081.59956183345</v>
       </c>
       <c r="E60" t="n">
-        <v>0.07173204604458076</v>
+        <v>0.06778232067774813</v>
       </c>
       <c r="F60" t="n">
-        <v>1.151739406022713</v>
+        <v>1.088322082820731</v>
       </c>
       <c r="G60" t="n">
-        <v>14.10080639929383</v>
+        <v>13.3243847607214</v>
       </c>
       <c r="H60" t="n">
-        <v>5.459453312118193e-07</v>
+        <v>5.158843718150801e-07</v>
       </c>
       <c r="I60" t="n">
-        <v>6.518815237845846e-06</v>
+        <v>6.159874829390006e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>58.97104056453676</v>
+        <v>55.72396442953414</v>
       </c>
       <c r="K60" t="n">
-        <v>2153.400843910179</v>
+        <v>2034.82982290703</v>
       </c>
       <c r="L60" t="n">
-        <v>0.008590473747403812</v>
+        <v>0.00811746323196217</v>
       </c>
       <c r="M60" t="n">
-        <v>3.02504207138024e-05</v>
+        <v>2.858476553401833e-05</v>
       </c>
       <c r="N60" t="n">
-        <v>2.383878820281494</v>
+        <v>2.25261717130986</v>
       </c>
       <c r="O60" t="n">
-        <v>291.9931901577994</v>
+        <v>275.9153982404758</v>
       </c>
       <c r="P60" t="n">
-        <v>9818.122279259138</v>
+        <v>9277.514715981857</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.472422597160541e-05</v>
+        <v>5.171098885627206e-05</v>
       </c>
     </row>
     <row r="61">
@@ -3767,52 +3767,52 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.307470254867938e-06</v>
+        <v>1.258620139018875e-07</v>
       </c>
       <c r="C61" t="n">
-        <v>0.00011</v>
+        <v>6e-06</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0209783998968634</v>
+        <v>0.001144276358010731</v>
       </c>
       <c r="E61" t="n">
-        <v>1.765175836558568e-07</v>
+        <v>9.628231835774006e-09</v>
       </c>
       <c r="F61" t="n">
-        <v>2.220526791989977e-07</v>
+        <v>1.211196431994533e-08</v>
       </c>
       <c r="G61" t="n">
-        <v>2.615899213066994e-06</v>
+        <v>1.42685411621836e-07</v>
       </c>
       <c r="H61" t="n">
-        <v>1.225647278715525e-12</v>
+        <v>6.685348792993775e-14</v>
       </c>
       <c r="I61" t="n">
-        <v>2.635696540369636e-11</v>
+        <v>1.437652658383438e-12</v>
       </c>
       <c r="J61" t="n">
-        <v>1.656715340150514e-05</v>
+        <v>9.036629128093717e-07</v>
       </c>
       <c r="K61" t="n">
-        <v>0.004311592743203601</v>
+        <v>0.0002351777859929237</v>
       </c>
       <c r="L61" t="n">
-        <v>5.254129810928953e-08</v>
+        <v>2.865888987779429e-09</v>
       </c>
       <c r="M61" t="n">
-        <v>1.839638491939014e-11</v>
+        <v>1.003439177421281e-12</v>
       </c>
       <c r="N61" t="n">
-        <v>7.382919905533107e-07</v>
+        <v>4.027047221199877e-08</v>
       </c>
       <c r="O61" t="n">
-        <v>9.02086821803393e-05</v>
+        <v>4.920473573473053e-06</v>
       </c>
       <c r="P61" t="n">
-        <v>0.001412965656907175</v>
+        <v>7.707085401311864e-05</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.042861902861423e-11</v>
+        <v>5.688337651971398e-13</v>
       </c>
     </row>
     <row r="62">
@@ -3877,52 +3877,52 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.849440255928273</v>
+        <v>1.848826842462314</v>
       </c>
       <c r="C63" t="n">
-        <v>22.01852899999998</v>
+        <v>22.01122599999989</v>
       </c>
       <c r="D63" t="n">
-        <v>17253.37988539132</v>
+        <v>17247.65736717475</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1441769812066815</v>
+        <v>0.1441291612776678</v>
       </c>
       <c r="F63" t="n">
-        <v>0.08808411915228061</v>
+        <v>0.08805490383448271</v>
       </c>
       <c r="G63" t="n">
-        <v>1.228217531420412</v>
+        <v>1.227810162125575</v>
       </c>
       <c r="H63" t="n">
-        <v>7.607826176167555e-07</v>
+        <v>7.605302848902357e-07</v>
       </c>
       <c r="I63" t="n">
-        <v>2.563544098689554e-05</v>
+        <v>2.56269383468904e-05</v>
       </c>
       <c r="J63" t="n">
-        <v>2.495466691923268</v>
+        <v>2.494639007510229</v>
       </c>
       <c r="K63" t="n">
-        <v>923.3343622049276</v>
+        <v>923.0281150960827</v>
       </c>
       <c r="L63" t="n">
-        <v>0.04603111744993651</v>
+        <v>0.04601585006987034</v>
       </c>
       <c r="M63" t="n">
-        <v>4.645094200688223e-06</v>
+        <v>4.643553538142234e-06</v>
       </c>
       <c r="N63" t="n">
-        <v>0.354827806468939</v>
+        <v>0.354710118885419</v>
       </c>
       <c r="O63" t="n">
-        <v>28.58992565193305</v>
+        <v>28.58044308263704</v>
       </c>
       <c r="P63" t="n">
-        <v>269.6945859968629</v>
+        <v>269.6051349912321</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.019157779196518e-06</v>
+        <v>3.0181563994376e-06</v>
       </c>
     </row>
     <row r="64">
@@ -3932,52 +3932,52 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.02269471963371652</v>
+        <v>0.0226949977684446</v>
       </c>
       <c r="C64" t="n">
-        <v>2.366287999999995</v>
+        <v>2.366316999999998</v>
       </c>
       <c r="D64" t="n">
-        <v>118.7416678439453</v>
+        <v>118.7431230803189</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0009644415924672946</v>
+        <v>0.0009644534121638764</v>
       </c>
       <c r="F64" t="n">
-        <v>0.005521923447783795</v>
+        <v>0.005521991121617244</v>
       </c>
       <c r="G64" t="n">
-        <v>0.05645209247410832</v>
+        <v>0.05645278432171181</v>
       </c>
       <c r="H64" t="n">
-        <v>8.421030611899132e-09</v>
+        <v>8.421133815688264e-09</v>
       </c>
       <c r="I64" t="n">
-        <v>1.379300259152519e-07</v>
+        <v>1.379317163142025e-07</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1289185948604934</v>
+        <v>0.1289201748200129</v>
       </c>
       <c r="K64" t="n">
-        <v>301.438385242775</v>
+        <v>301.4420795154811</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00015573671662963</v>
+        <v>0.0001557386252581583</v>
       </c>
       <c r="M64" t="n">
-        <v>4.376325964123807e-07</v>
+        <v>4.376379598107909e-07</v>
       </c>
       <c r="N64" t="n">
-        <v>0.01655008943392184</v>
+        <v>0.01655029226324508</v>
       </c>
       <c r="O64" t="n">
-        <v>0.938456444122126</v>
+        <v>0.9384679453581899</v>
       </c>
       <c r="P64" t="n">
-        <v>24.33548318354226</v>
+        <v>24.3357814266185</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.169691909729419e-07</v>
+        <v>2.169718500349577e-07</v>
       </c>
     </row>
     <row r="65">
@@ -3987,52 +3987,52 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4.780196615510732e-07</v>
+        <v>5.19586588642471e-08</v>
       </c>
       <c r="C65" t="n">
-        <v>4.6e-05</v>
+        <v>5.000000000000001e-06</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00329598167337448</v>
+        <v>0.0003582588775407045</v>
       </c>
       <c r="E65" t="n">
-        <v>2.328778733231958e-08</v>
+        <v>2.531281231773868e-09</v>
       </c>
       <c r="F65" t="n">
-        <v>9.505192273570036e-08</v>
+        <v>1.033173073214135e-08</v>
       </c>
       <c r="G65" t="n">
-        <v>6.4893423553257e-07</v>
+        <v>7.053632994919242e-08</v>
       </c>
       <c r="H65" t="n">
-        <v>1.271237102555894e-12</v>
+        <v>1.381779459299885e-13</v>
       </c>
       <c r="I65" t="n">
-        <v>3.59819713700391e-12</v>
+        <v>3.911083844569469e-13</v>
       </c>
       <c r="J65" t="n">
-        <v>9.44454154862453e-06</v>
+        <v>1.026580603111362e-06</v>
       </c>
       <c r="K65" t="n">
-        <v>0.000636076447636037</v>
+        <v>6.913874430826493e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>4.770329622216892e-09</v>
+        <v>5.185140893714015e-10</v>
       </c>
       <c r="M65" t="n">
-        <v>5.762681961177663e-12</v>
+        <v>6.263784740410505e-13</v>
       </c>
       <c r="N65" t="n">
-        <v>2.363762119579833e-07</v>
+        <v>2.569306651717211e-08</v>
       </c>
       <c r="O65" t="n">
-        <v>4.030669397971684e-05</v>
+        <v>4.381162389099658e-06</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0006380395619550058</v>
+        <v>6.935212629945718e-05</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.534521479663844e-12</v>
+        <v>3.841871173547657e-13</v>
       </c>
     </row>
     <row r="66">
@@ -4042,52 +4042,52 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.198283538233443e-05</v>
+        <v>1.917253661173657e-06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.001574999999999878</v>
+        <v>0.000252</v>
       </c>
       <c r="D66" t="n">
-        <v>0.04036653225572492</v>
+        <v>0.006458645160916487</v>
       </c>
       <c r="E66" t="n">
-        <v>2.091592256033508e-07</v>
+        <v>3.346547609653872e-08</v>
       </c>
       <c r="F66" t="n">
-        <v>3.358288736262423e-06</v>
+        <v>5.373261978020294e-07</v>
       </c>
       <c r="G66" t="n">
-        <v>4.111570643093182e-05</v>
+        <v>6.578513028949601e-06</v>
       </c>
       <c r="H66" t="n">
-        <v>1.591889664307897e-12</v>
+        <v>2.547023462892832e-13</v>
       </c>
       <c r="I66" t="n">
-        <v>1.900782735447836e-11</v>
+        <v>3.041252376716773e-12</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0001719501653394446</v>
+        <v>2.751202645431327e-05</v>
       </c>
       <c r="K66" t="n">
-        <v>0.006278974011781769</v>
+        <v>0.001004635841885161</v>
       </c>
       <c r="L66" t="n">
-        <v>2.504845373372194e-08</v>
+        <v>4.007752597395821e-09</v>
       </c>
       <c r="M66" t="n">
-        <v>8.820541054610557e-11</v>
+        <v>1.411286568737798e-11</v>
       </c>
       <c r="N66" t="n">
-        <v>6.951011095827703e-06</v>
+        <v>1.112161775332519e-06</v>
       </c>
       <c r="O66" t="n">
-        <v>0.0008514056534355757</v>
+        <v>0.0001362249045497027</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0286280813952049</v>
+        <v>0.004580493023233138</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.59567130133753e-10</v>
+        <v>2.553074082140246e-11</v>
       </c>
     </row>
     <row r="67">
@@ -4097,52 +4097,52 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.209481354498146e-06</v>
+        <v>7.551720834113283e-07</v>
       </c>
       <c r="C67" t="n">
-        <v>0.000153</v>
+        <v>3.6e-05</v>
       </c>
       <c r="D67" t="n">
-        <v>0.02917904712927374</v>
+        <v>0.006865658148064408</v>
       </c>
       <c r="E67" t="n">
-        <v>2.455199118122376e-07</v>
+        <v>5.776939101464414e-08</v>
       </c>
       <c r="F67" t="n">
-        <v>3.088550901586064e-07</v>
+        <v>7.267178591967208e-08</v>
       </c>
       <c r="G67" t="n">
-        <v>3.63847799635683e-06</v>
+        <v>8.561124697310186e-07</v>
       </c>
       <c r="H67" t="n">
-        <v>1.704763942213441e-12</v>
+        <v>4.011209275796332e-13</v>
       </c>
       <c r="I67" t="n">
-        <v>3.66601427887805e-11</v>
+        <v>8.625915950301292e-12</v>
       </c>
       <c r="J67" t="n">
-        <v>2.304340427663903e-05</v>
+        <v>5.42197747685624e-06</v>
       </c>
       <c r="K67" t="n">
-        <v>0.005997033542819562</v>
+        <v>0.001411066715957544</v>
       </c>
       <c r="L67" t="n">
-        <v>7.308016918837567e-08</v>
+        <v>1.719533392667663e-08</v>
       </c>
       <c r="M67" t="n">
-        <v>2.558769902424274e-11</v>
+        <v>6.020635064527703e-12</v>
       </c>
       <c r="N67" t="n">
-        <v>1.026897041405971e-06</v>
+        <v>2.416228332719933e-07</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0001254720761235631</v>
+        <v>2.952284144083838e-05</v>
       </c>
       <c r="P67" t="n">
-        <v>0.001965306777334529</v>
+        <v>0.0004624251240787127</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.450526101252708e-11</v>
+        <v>3.413002591182842e-12</v>
       </c>
     </row>
     <row r="68">
@@ -4262,52 +4262,52 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1323762091153549</v>
+        <v>0.1237125289995335</v>
       </c>
       <c r="C70" t="n">
-        <v>12.86035599999999</v>
+        <v>12.018679</v>
       </c>
       <c r="D70" t="n">
-        <v>689.6904698848534</v>
+        <v>644.5520144936287</v>
       </c>
       <c r="E70" t="n">
-        <v>0.005768281035446497</v>
+        <v>0.005390761977881414</v>
       </c>
       <c r="F70" t="n">
-        <v>0.03347210565231521</v>
+        <v>0.03128144300898531</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3307899397723786</v>
+        <v>0.3091405947513081</v>
       </c>
       <c r="H70" t="n">
-        <v>4.314739677452463e-08</v>
+        <v>4.032351138013964e-08</v>
       </c>
       <c r="I70" t="n">
-        <v>7.524235570810999e-07</v>
+        <v>7.031793835719572e-07</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7046956260068793</v>
+        <v>0.6585751220013457</v>
       </c>
       <c r="K70" t="n">
-        <v>534.4058500628524</v>
+        <v>499.4303709498832</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0009616255949169737</v>
+        <v>0.0008986896897326281</v>
       </c>
       <c r="M70" t="n">
-        <v>2.168981586889729e-06</v>
+        <v>2.027027358320273e-06</v>
       </c>
       <c r="N70" t="n">
-        <v>0.09365334771750765</v>
+        <v>0.08752397861242003</v>
       </c>
       <c r="O70" t="n">
-        <v>6.718420352688866</v>
+        <v>6.278717137071034</v>
       </c>
       <c r="P70" t="n">
-        <v>131.5865178601978</v>
+        <v>122.9745209922249</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.18189413805739e-06</v>
+        <v>1.104542227080919e-06</v>
       </c>
     </row>
     <row r="71">
@@ -4317,52 +4317,52 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0193998029897434</v>
+        <v>0.02026673095763436</v>
       </c>
       <c r="C71" t="n">
-        <v>4.004366999999999</v>
+        <v>4.183312</v>
       </c>
       <c r="D71" t="n">
-        <v>141.9211040848139</v>
+        <v>148.2631980962911</v>
       </c>
       <c r="E71" t="n">
-        <v>0.001270375264804146</v>
+        <v>0.001327145111763822</v>
       </c>
       <c r="F71" t="n">
-        <v>0.004284024571002211</v>
+        <v>0.004475466758208826</v>
       </c>
       <c r="G71" t="n">
-        <v>0.04273235062964498</v>
+        <v>0.04464195094435686</v>
       </c>
       <c r="H71" t="n">
-        <v>6.596048084404522e-08</v>
+        <v>6.890808735579544e-08</v>
       </c>
       <c r="I71" t="n">
-        <v>7.119301969834624e-07</v>
+        <v>7.437445509373348e-07</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2724171929466714</v>
+        <v>0.2845908260307125</v>
       </c>
       <c r="K71" t="n">
-        <v>29.85225553463848</v>
+        <v>31.18627708327423</v>
       </c>
       <c r="L71" t="n">
-        <v>4.268015165764927e-05</v>
+        <v>4.458741933275949e-05</v>
       </c>
       <c r="M71" t="n">
-        <v>4.779628191875666e-07</v>
+        <v>4.99321764728652e-07</v>
       </c>
       <c r="N71" t="n">
-        <v>0.01886883780992689</v>
+        <v>0.01971203829127572</v>
       </c>
       <c r="O71" t="n">
-        <v>1.326717192275682</v>
+        <v>1.386004817004328</v>
       </c>
       <c r="P71" t="n">
-        <v>47.01957795951377</v>
+        <v>49.12076358459889</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.511708983977858e-07</v>
+        <v>2.623950884916987e-07</v>
       </c>
     </row>
     <row r="72">
@@ -4372,52 +4372,52 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.422330794073495e-08</v>
+        <v>4.84466158814699e-09</v>
       </c>
       <c r="C72" t="n">
-        <v>5e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0001772079133665994</v>
+        <v>3.544158267331987e-05</v>
       </c>
       <c r="E72" t="n">
-        <v>1.586237306425892e-09</v>
+        <v>3.172474612851784e-10</v>
       </c>
       <c r="F72" t="n">
-        <v>5.349190734768081e-09</v>
+        <v>1.069838146953616e-09</v>
       </c>
       <c r="G72" t="n">
-        <v>5.33571855796996e-08</v>
+        <v>1.067143711593992e-08</v>
       </c>
       <c r="H72" t="n">
-        <v>8.236068377854132e-14</v>
+        <v>1.647213675570826e-14</v>
       </c>
       <c r="I72" t="n">
-        <v>8.889422435349489e-13</v>
+        <v>1.777884487069898e-13</v>
       </c>
       <c r="J72" t="n">
-        <v>3.401501322764265e-07</v>
+        <v>6.803002645528529e-08</v>
       </c>
       <c r="K72" t="n">
-        <v>3.72746248466218e-05</v>
+        <v>7.454924969324359e-06</v>
       </c>
       <c r="L72" t="n">
-        <v>5.329200802230325e-11</v>
+        <v>1.065840160446065e-11</v>
       </c>
       <c r="M72" t="n">
-        <v>5.968019654386907e-13</v>
+        <v>1.193603930877381e-13</v>
       </c>
       <c r="N72" t="n">
-        <v>2.356032527728714e-08</v>
+        <v>4.712065055457427e-09</v>
       </c>
       <c r="O72" t="n">
-        <v>1.656587910493322e-06</v>
+        <v>3.313175820986644e-07</v>
       </c>
       <c r="P72" t="n">
-        <v>5.871037539705249e-05</v>
+        <v>1.17420750794105e-05</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.136212270226303e-13</v>
+        <v>6.272424540452605e-14</v>
       </c>
     </row>
     <row r="73">
@@ -4427,52 +4427,52 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.08743064704736576</v>
+        <v>0.08976353270679176</v>
       </c>
       <c r="C73" t="n">
-        <v>9.329340999999999</v>
+        <v>9.578272999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>433.056793641175</v>
+        <v>444.6119178192585</v>
       </c>
       <c r="E73" t="n">
-        <v>0.003763111203335857</v>
+        <v>0.003863521167776947</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01545624032736267</v>
+        <v>0.01586865453938161</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1374022664112583</v>
+        <v>0.1410685297606511</v>
       </c>
       <c r="H73" t="n">
-        <v>9.848112685102625e-08</v>
+        <v>1.011088691394987e-07</v>
       </c>
       <c r="I73" t="n">
-        <v>5.656618836824414e-07</v>
+        <v>5.807552695956413e-07</v>
       </c>
       <c r="J73" t="n">
-        <v>0.7349510261893339</v>
+        <v>0.754561503376454</v>
       </c>
       <c r="K73" t="n">
-        <v>227.4932891991316</v>
+        <v>233.5634242136968</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0003819750133486146</v>
+        <v>0.0003921671377465648</v>
       </c>
       <c r="M73" t="n">
-        <v>1.200829937918132e-06</v>
+        <v>1.23287132198865e-06</v>
       </c>
       <c r="N73" t="n">
-        <v>0.05203160453062548</v>
+        <v>0.05341994818523278</v>
       </c>
       <c r="O73" t="n">
-        <v>7.93646536271199</v>
+        <v>8.148231681005063</v>
       </c>
       <c r="P73" t="n">
-        <v>113.9767220207648</v>
+        <v>117.0179286146789</v>
       </c>
       <c r="Q73" t="n">
-        <v>8.606187654846963e-07</v>
+        <v>8.835823971634652e-07</v>
       </c>
     </row>
     <row r="74">
@@ -4482,52 +4482,52 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.686884043420196e-07</v>
+        <v>2.811473405700327e-08</v>
       </c>
       <c r="C74" t="n">
-        <v>1.8e-05</v>
+        <v>3e-06</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0008355383606989077</v>
+        <v>0.000139256393449818</v>
       </c>
       <c r="E74" t="n">
-        <v>7.260534442898516e-09</v>
+        <v>1.210089073816419e-09</v>
       </c>
       <c r="F74" t="n">
-        <v>2.982121951513264e-08</v>
+        <v>4.970203252522106e-09</v>
       </c>
       <c r="G74" t="n">
-        <v>2.651034832366665e-07</v>
+        <v>4.418391387277774e-08</v>
       </c>
       <c r="H74" t="n">
-        <v>1.900091639182665e-13</v>
+        <v>3.166819398637774e-14</v>
       </c>
       <c r="I74" t="n">
-        <v>1.091386187542817e-12</v>
+        <v>1.818976979238028e-13</v>
       </c>
       <c r="J74" t="n">
-        <v>1.418012105185993e-06</v>
+        <v>2.363353508643321e-07</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0004389248078277304</v>
+        <v>7.315413463795507e-05</v>
       </c>
       <c r="L74" t="n">
-        <v>7.369813409409071e-10</v>
+        <v>1.228302234901512e-10</v>
       </c>
       <c r="M74" t="n">
-        <v>2.316877353129911e-12</v>
+        <v>3.861462255216518e-13</v>
       </c>
       <c r="N74" t="n">
-        <v>1.00389607535115e-07</v>
+        <v>1.67316012558525e-08</v>
       </c>
       <c r="O74" t="n">
-        <v>1.531259030287512e-05</v>
+        <v>2.55209838381252e-06</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0002199063145375182</v>
+        <v>3.66510524229197e-05</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.660475030200366e-12</v>
+        <v>2.767458383667277e-13</v>
       </c>
     </row>
     <row r="75">
@@ -4537,52 +4537,52 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.3692728560674667</v>
+        <v>0.4650107803368573</v>
       </c>
       <c r="C75" t="n">
-        <v>39.405886</v>
+        <v>49.62228199999998</v>
       </c>
       <c r="D75" t="n">
-        <v>2350.881359766046</v>
+        <v>2960.372411950188</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0208004454744305</v>
+        <v>0.02619318268996195</v>
       </c>
       <c r="F75" t="n">
-        <v>0.04988036426303388</v>
+        <v>0.0628123804074089</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5197091721915348</v>
+        <v>0.6544493150204741</v>
       </c>
       <c r="H75" t="n">
-        <v>1.625652320256724e-07</v>
+        <v>2.047120013231867e-07</v>
       </c>
       <c r="I75" t="n">
-        <v>2.654941464986066e-06</v>
+        <v>3.343263340634738e-06</v>
       </c>
       <c r="J75" t="n">
-        <v>3.053845333889173</v>
+        <v>3.845587289742264</v>
       </c>
       <c r="K75" t="n">
-        <v>322.1931938381712</v>
+        <v>405.7252138200469</v>
       </c>
       <c r="L75" t="n">
-        <v>0.003038776699295554</v>
+        <v>0.003826611951003288</v>
       </c>
       <c r="M75" t="n">
-        <v>3.931866899647637e-06</v>
+        <v>4.95124530586067e-06</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1723235014465917</v>
+        <v>0.2170002061115991</v>
       </c>
       <c r="O75" t="n">
-        <v>15.71815869956519</v>
+        <v>19.79325889311503</v>
       </c>
       <c r="P75" t="n">
-        <v>458.1599081278527</v>
+        <v>576.942748152253</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.83133350661336e-06</v>
+        <v>3.56538689933826e-06</v>
       </c>
     </row>
     <row r="76">
@@ -4592,52 +4592,52 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.594539813057172e-08</v>
+        <v>4.324233021761951e-09</v>
       </c>
       <c r="C76" t="n">
-        <v>6.000000000000001e-06</v>
+        <v>9.999999999999997e-07</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0001618420248223232</v>
+        <v>2.697367080372052e-05</v>
       </c>
       <c r="E76" t="n">
-        <v>1.498346477842254e-09</v>
+        <v>2.497244129737088e-10</v>
       </c>
       <c r="F76" t="n">
-        <v>7.651326905143823e-09</v>
+        <v>1.275221150857303e-09</v>
       </c>
       <c r="G76" t="n">
-        <v>7.257764224273853e-08</v>
+        <v>1.209627370712308e-08</v>
       </c>
       <c r="H76" t="n">
-        <v>2.883484476151954e-14</v>
+        <v>4.805807460253255e-15</v>
       </c>
       <c r="I76" t="n">
-        <v>1.495303907155435e-13</v>
+        <v>2.492173178592391e-14</v>
       </c>
       <c r="J76" t="n">
-        <v>3.167044386273277e-07</v>
+        <v>5.278407310455459e-08</v>
       </c>
       <c r="K76" t="n">
-        <v>7.142244515087265e-05</v>
+        <v>1.190374085847877e-05</v>
       </c>
       <c r="L76" t="n">
-        <v>6.226483016854771e-11</v>
+        <v>1.037747169475795e-11</v>
       </c>
       <c r="M76" t="n">
-        <v>7.256426814779397e-13</v>
+        <v>1.209404469129899e-13</v>
       </c>
       <c r="N76" t="n">
-        <v>2.58082529864754e-08</v>
+        <v>4.301375497745899e-09</v>
       </c>
       <c r="O76" t="n">
-        <v>2.828907382107922e-06</v>
+        <v>4.714845636846535e-07</v>
       </c>
       <c r="P76" t="n">
-        <v>6.463748636002389e-05</v>
+        <v>1.077291439333731e-05</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.943470320887243e-13</v>
+        <v>1.157245053481207e-13</v>
       </c>
     </row>
     <row r="77">
@@ -4647,52 +4647,52 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9.175731503818134e-08</v>
+        <v>1.529288583969689e-08</v>
       </c>
       <c r="C77" t="n">
-        <v>1.2e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="D77" t="n">
-        <v>0.000522459226309386</v>
+        <v>8.707653771823102e-05</v>
       </c>
       <c r="E77" t="n">
-        <v>4.738591443857763e-09</v>
+        <v>7.897652406429605e-10</v>
       </c>
       <c r="F77" t="n">
-        <v>1.793476313852101e-08</v>
+        <v>2.989127189753503e-09</v>
       </c>
       <c r="G77" t="n">
-        <v>1.548232781951303e-07</v>
+        <v>2.580387969918839e-08</v>
       </c>
       <c r="H77" t="n">
-        <v>1.277144573585513e-13</v>
+        <v>2.128574289309188e-14</v>
       </c>
       <c r="I77" t="n">
-        <v>6.898801233412457e-13</v>
+        <v>1.149800205568743e-13</v>
       </c>
       <c r="J77" t="n">
-        <v>8.922091345000976e-07</v>
+        <v>1.48701522416683e-07</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0002201385982731789</v>
+        <v>3.668976637886316e-05</v>
       </c>
       <c r="L77" t="n">
-        <v>4.139279232615212e-10</v>
+        <v>6.898798721025355e-11</v>
       </c>
       <c r="M77" t="n">
-        <v>1.434185932217998e-12</v>
+        <v>2.390309887029997e-13</v>
       </c>
       <c r="N77" t="n">
-        <v>6.227457261842723e-08</v>
+        <v>1.037909543640454e-08</v>
       </c>
       <c r="O77" t="n">
-        <v>9.948565627901776e-06</v>
+        <v>1.658094271316963e-06</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0001373406616284878</v>
+        <v>2.289011027141463e-05</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.544333565738449e-11</v>
+        <v>1.090722260956408e-11</v>
       </c>
     </row>
     <row r="78">
@@ -4702,52 +4702,52 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3.376434896606751e-05</v>
+        <v>0.0004749493847464906</v>
       </c>
       <c r="C78" t="n">
-        <v>0.004579999999999941</v>
+        <v>0.06442499999999998</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2763704695622675</v>
+        <v>3.887591157543516</v>
       </c>
       <c r="E78" t="n">
-        <v>1.808767304579459e-06</v>
+        <v>2.544319510863169e-05</v>
       </c>
       <c r="F78" t="n">
-        <v>4.952013188777785e-06</v>
+        <v>6.965795844694602e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>5.513228094897829e-05</v>
+        <v>0.0007755234061436617</v>
       </c>
       <c r="H78" t="n">
-        <v>1.352755777731232e-10</v>
+        <v>1.902866615291173e-09</v>
       </c>
       <c r="I78" t="n">
-        <v>4.025026227515912e-10</v>
+        <v>5.66184093248288e-09</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0004723158506944272</v>
+        <v>0.006643875257857828</v>
       </c>
       <c r="K78" t="n">
-        <v>0.05732641327685742</v>
+        <v>0.8063873745330973</v>
       </c>
       <c r="L78" t="n">
-        <v>4.36169894819218e-07</v>
+        <v>6.135424775923247e-06</v>
       </c>
       <c r="M78" t="n">
-        <v>5.211440416058894e-10</v>
+        <v>7.330721589620054e-09</v>
       </c>
       <c r="N78" t="n">
-        <v>1.816520590072564e-05</v>
+        <v>0.00025552257426949</v>
       </c>
       <c r="O78" t="n">
-        <v>0.002363087243552736</v>
+        <v>0.03324058857333776</v>
       </c>
       <c r="P78" t="n">
-        <v>0.04595318532592956</v>
+        <v>0.6464047957692247</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.703916180790634e-10</v>
+        <v>3.803489081821808e-09</v>
       </c>
     </row>
     <row r="79">
@@ -4757,52 +4757,52 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4.06812315981711e-05</v>
+        <v>1.575803285603969e-05</v>
       </c>
       <c r="C79" t="n">
-        <v>0.001881999999999998</v>
+        <v>0.0007289999999999984</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3658873715982353</v>
+        <v>0.1417278926116435</v>
       </c>
       <c r="E79" t="n">
-        <v>3.260496157785856e-06</v>
+        <v>1.262965833701321e-06</v>
       </c>
       <c r="F79" t="n">
-        <v>4.049961176149374e-06</v>
+        <v>1.56876817078262e-06</v>
       </c>
       <c r="G79" t="n">
-        <v>4.038313474759339e-05</v>
+        <v>1.564256388469476e-05</v>
       </c>
       <c r="H79" t="n">
-        <v>2.643078407238126e-11</v>
+        <v>1.023806673154406e-11</v>
       </c>
       <c r="I79" t="n">
-        <v>5.518413919093816e-10</v>
+        <v>2.137579036673425e-10</v>
       </c>
       <c r="J79" t="n">
-        <v>0.000149080427233303</v>
+        <v>5.774688174977563e-05</v>
       </c>
       <c r="K79" t="n">
-        <v>0.03029698993029934</v>
+        <v>0.01173565656705005</v>
       </c>
       <c r="L79" t="n">
-        <v>8.339643978941967e-07</v>
+        <v>3.230393443490268e-07</v>
       </c>
       <c r="M79" t="n">
-        <v>2.84661018908485e-10</v>
+        <v>1.102645498322451e-10</v>
       </c>
       <c r="N79" t="n">
-        <v>1.442975264935596e-05</v>
+        <v>5.589420659607056e-06</v>
       </c>
       <c r="O79" t="n">
-        <v>0.001936314478079269</v>
+        <v>0.0007500389237618414</v>
       </c>
       <c r="P79" t="n">
-        <v>0.02186301105312694</v>
+        <v>0.008468722134819084</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.481979738332176e-10</v>
+        <v>5.740506000234618e-11</v>
       </c>
     </row>
     <row r="80">
@@ -4812,52 +4812,52 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4.195400463396253e-08</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0003814254526702435</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>3.209410611924669e-09</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>4.037321439981777e-09</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>4.75618038739453e-08</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2.228449597664634e-14</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>4.792175527945281e-13</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>3.01220970936457e-07</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>7.839259533097453e-05</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>9.552963292598094e-10</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.344797258070936e-13</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.342349073733291e-08</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1.640157857824354e-06</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.569028467103955e-05</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.896112550657131e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4867,52 +4867,52 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0001946468955057811</v>
+        <v>3.61158854348863e-05</v>
       </c>
       <c r="C81" t="n">
-        <v>0.02558399999999479</v>
+        <v>0.004747</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6557062610986257</v>
+        <v>0.1216634467415498</v>
       </c>
       <c r="E81" t="n">
-        <v>3.397542620847913e-06</v>
+        <v>6.303992659931334e-07</v>
       </c>
       <c r="F81" t="n">
-        <v>5.455140255779497e-05</v>
+        <v>1.01217756387549e-05</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0006678757037008426</v>
+        <v>0.0001239214339223165</v>
       </c>
       <c r="H81" t="n">
-        <v>2.585835248993518e-11</v>
+        <v>4.797904912044531e-12</v>
       </c>
       <c r="I81" t="n">
-        <v>3.087595270075423e-10</v>
+        <v>5.72889882233076e-11</v>
       </c>
       <c r="J81" t="n">
-        <v>0.002793125733361147</v>
+        <v>0.0005182523395977198</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1019944578523204</v>
+        <v>0.01892462833900342</v>
       </c>
       <c r="L81" t="n">
-        <v>4.068823113164815e-07</v>
+        <v>7.549524436443602e-08</v>
       </c>
       <c r="M81" t="n">
-        <v>1.432791887880167e-09</v>
+        <v>2.658483072142174e-10</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0001129109002384975</v>
+        <v>2.09501267758074e-05</v>
       </c>
       <c r="O81" t="n">
-        <v>0.01383007126190038</v>
+        <v>0.002566109610704129</v>
       </c>
       <c r="P81" t="n">
-        <v>0.4650291012157654</v>
+        <v>0.08628412849717353</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.591978068151957e-09</v>
+        <v>4.809302645997438e-10</v>
       </c>
     </row>
     <row r="82">
@@ -4922,52 +4922,52 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3.784350019664331</v>
+        <v>4.183910960664194</v>
       </c>
       <c r="C82" t="n">
-        <v>180.40471</v>
+        <v>199.4522809999999</v>
       </c>
       <c r="D82" t="n">
-        <v>34405.47408779702</v>
+        <v>38038.08828326881</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2894963953575962</v>
+        <v>0.3200621336069904</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3641759017783474</v>
+        <v>0.4026264851672848</v>
       </c>
       <c r="G82" t="n">
-        <v>4.290186717477994</v>
+        <v>4.743155135566517</v>
       </c>
       <c r="H82" t="n">
-        <v>2.010114017081486e-06</v>
+        <v>2.222346776738674e-06</v>
       </c>
       <c r="I82" t="n">
-        <v>4.322655181939887e-05</v>
+        <v>4.77905170000484e-05</v>
       </c>
       <c r="J82" t="n">
-        <v>27.170840953855</v>
+        <v>30.03960486915554</v>
       </c>
       <c r="K82" t="n">
-        <v>7071.19671341591</v>
+        <v>7817.790976136412</v>
       </c>
       <c r="L82" t="n">
-        <v>0.08616997862209025</v>
+        <v>0.09526801595089801</v>
       </c>
       <c r="M82" t="n">
-        <v>3.017085896755411e-05</v>
+        <v>3.335637213023967e-05</v>
       </c>
       <c r="N82" t="n">
-        <v>1.210830476828116</v>
+        <v>1.338672923271711</v>
       </c>
       <c r="O82" t="n">
-        <v>147.9461013475116</v>
+        <v>163.5666129715702</v>
       </c>
       <c r="P82" t="n">
-        <v>2317.324177948167</v>
+        <v>2561.992938589085</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.710338174143302e-05</v>
+        <v>1.890919866306465e-05</v>
       </c>
     </row>
     <row r="83">
@@ -5032,52 +5032,52 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.622125289622657e-06</v>
+        <v>2.727010301207563e-07</v>
       </c>
       <c r="C84" t="n">
-        <v>0.000125</v>
+        <v>1.3e-05</v>
       </c>
       <c r="D84" t="n">
-        <v>0.02383909079189023</v>
+        <v>0.002479265442356584</v>
       </c>
       <c r="E84" t="n">
-        <v>2.005881632452918e-07</v>
+        <v>2.086116897751034e-08</v>
       </c>
       <c r="F84" t="n">
-        <v>2.523325899988611e-07</v>
+        <v>2.624258935988154e-08</v>
       </c>
       <c r="G84" t="n">
-        <v>2.972612742121585e-06</v>
+        <v>3.091517251806448e-07</v>
       </c>
       <c r="H84" t="n">
-        <v>1.39278099854037e-12</v>
+        <v>1.448492238481984e-13</v>
       </c>
       <c r="I84" t="n">
-        <v>2.995109704965496e-11</v>
+        <v>3.114914093164115e-12</v>
       </c>
       <c r="J84" t="n">
-        <v>1.882631068352858e-05</v>
+        <v>1.957936311086972e-06</v>
       </c>
       <c r="K84" t="n">
-        <v>0.004899537208185912</v>
+        <v>0.0005095518696513347</v>
       </c>
       <c r="L84" t="n">
-        <v>5.970602057873812e-08</v>
+        <v>6.209426140188763e-09</v>
       </c>
       <c r="M84" t="n">
-        <v>2.090498286294335e-11</v>
+        <v>2.174118217746108e-12</v>
       </c>
       <c r="N84" t="n">
-        <v>8.389681710833078e-07</v>
+        <v>8.725268979266398e-08</v>
       </c>
       <c r="O84" t="n">
-        <v>0.000102509866114022</v>
+        <v>1.066102607585828e-05</v>
       </c>
       <c r="P84" t="n">
-        <v>0.001605642791939972</v>
+        <v>0.000166986850361757</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.185070344160708e-11</v>
+        <v>1.232473157927136e-12</v>
       </c>
     </row>
     <row r="85">
@@ -5087,52 +5087,52 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.396253441001159e-05</v>
+        <v>2.327089068335265e-06</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0007860000000000001</v>
+        <v>0.000131</v>
       </c>
       <c r="D85" t="n">
-        <v>0.09316352659913056</v>
+        <v>0.01552725443318843</v>
       </c>
       <c r="E85" t="n">
-        <v>7.563808065970172e-07</v>
+        <v>1.260634677661695e-07</v>
       </c>
       <c r="F85" t="n">
-        <v>1.430546510283665e-06</v>
+        <v>2.384244183806109e-07</v>
       </c>
       <c r="G85" t="n">
-        <v>1.384710547596037e-05</v>
+        <v>2.307850912660061e-06</v>
       </c>
       <c r="H85" t="n">
-        <v>9.760489817458198e-12</v>
+        <v>1.6267483029097e-12</v>
       </c>
       <c r="I85" t="n">
-        <v>1.291174595115295e-10</v>
+        <v>2.151957658525492e-11</v>
       </c>
       <c r="J85" t="n">
-        <v>0.000218410698693305</v>
+        <v>3.640178311555083e-05</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01018767709006091</v>
+        <v>0.001697946181676819</v>
       </c>
       <c r="L85" t="n">
-        <v>2.868490074682736e-07</v>
+        <v>4.780816791137893e-08</v>
       </c>
       <c r="M85" t="n">
-        <v>1.039687860365844e-10</v>
+        <v>1.732813100609739e-11</v>
       </c>
       <c r="N85" t="n">
-        <v>3.916937313068076e-06</v>
+        <v>6.52822885511346e-07</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003485968562303444</v>
+        <v>0.0005809947603839074</v>
       </c>
       <c r="P85" t="n">
-        <v>0.01295566162105921</v>
+        <v>0.002159276936843201</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.19028621379736e-10</v>
+        <v>1.983810356328934e-11</v>
       </c>
     </row>
     <row r="86">
@@ -5142,52 +5142,52 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.727002210525737</v>
+        <v>2.727000088543027</v>
       </c>
       <c r="C86" t="n">
-        <v>546.1759579999999</v>
+        <v>546.175533</v>
       </c>
       <c r="D86" t="n">
-        <v>12460.39765218263</v>
+        <v>12460.38795627982</v>
       </c>
       <c r="E86" t="n">
-        <v>0.08011439718299368</v>
+        <v>0.08011433484297614</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9584226887368372</v>
+        <v>0.9584219429521927</v>
       </c>
       <c r="G86" t="n">
-        <v>9.380547282635543</v>
+        <v>9.380539983279839</v>
       </c>
       <c r="H86" t="n">
-        <v>2.101396604013001e-06</v>
+        <v>2.10139496883748e-06</v>
       </c>
       <c r="I86" t="n">
-        <v>1.172747420613332e-05</v>
+        <v>1.172746508054574e-05</v>
       </c>
       <c r="J86" t="n">
-        <v>34.26554118504416</v>
+        <v>34.26551452174127</v>
       </c>
       <c r="K86" t="n">
-        <v>6726.348772126265</v>
+        <v>6726.34353810198</v>
       </c>
       <c r="L86" t="n">
-        <v>0.007819103153823901</v>
+        <v>0.007819097069486441</v>
       </c>
       <c r="M86" t="n">
-        <v>9.082780966097821e-05</v>
+        <v>9.082773898445257e-05</v>
       </c>
       <c r="N86" t="n">
-        <v>2.496178143895708</v>
+        <v>2.496176201525863</v>
       </c>
       <c r="O86" t="n">
-        <v>225.2094445827579</v>
+        <v>225.2092693388414</v>
       </c>
       <c r="P86" t="n">
-        <v>4417.341608504451</v>
+        <v>4417.338171205251</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.751286682912058e-05</v>
+        <v>4.751282985757669e-05</v>
       </c>
     </row>
     <row r="87">
@@ -5197,52 +5197,52 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7.411497131239594</v>
+        <v>7.39445106374529</v>
       </c>
       <c r="C87" t="n">
-        <v>822.4033530000002</v>
+        <v>820.5118670000002</v>
       </c>
       <c r="D87" t="n">
-        <v>51088.59348064867</v>
+        <v>50971.0923068319</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4021783519574609</v>
+        <v>0.4012533621462501</v>
       </c>
       <c r="F87" t="n">
-        <v>1.466721926307716</v>
+        <v>1.463348540268634</v>
       </c>
       <c r="G87" t="n">
-        <v>12.14717536923923</v>
+        <v>12.11923748198884</v>
       </c>
       <c r="H87" t="n">
-        <v>1.90331017730367e-06</v>
+        <v>1.898932660430843e-06</v>
       </c>
       <c r="I87" t="n">
-        <v>5.687474672774805e-05</v>
+        <v>5.674393769493385e-05</v>
       </c>
       <c r="J87" t="n">
-        <v>97.49490859792816</v>
+        <v>97.27067525304749</v>
       </c>
       <c r="K87" t="n">
-        <v>10064.45882489922</v>
+        <v>10041.31108006643</v>
       </c>
       <c r="L87" t="n">
-        <v>0.08846339877492634</v>
+        <v>0.08825993744456477</v>
       </c>
       <c r="M87" t="n">
-        <v>8.763302662800665e-05</v>
+        <v>8.743147511146692e-05</v>
       </c>
       <c r="N87" t="n">
-        <v>3.974684484694986</v>
+        <v>3.96554291197426</v>
       </c>
       <c r="O87" t="n">
-        <v>1092.306882461742</v>
+        <v>1089.794632033356</v>
       </c>
       <c r="P87" t="n">
-        <v>10536.46500980474</v>
+        <v>10512.2316746866</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0001374146815296215</v>
+        <v>0.0001370986347317095</v>
       </c>
     </row>
     <row r="88">
@@ -5252,52 +5252,52 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.055701641162909e-07</v>
+        <v>1.909813525726818e-08</v>
       </c>
       <c r="C88" t="n">
-        <v>1.6e-05</v>
+        <v>1e-06</v>
       </c>
       <c r="D88" t="n">
-        <v>0.002680362815992558</v>
+        <v>0.0001675226759995349</v>
       </c>
       <c r="E88" t="n">
-        <v>2.251455238307346e-08</v>
+        <v>1.407159523942091e-09</v>
       </c>
       <c r="F88" t="n">
-        <v>3.31302118955779e-08</v>
+        <v>2.070638243473619e-09</v>
       </c>
       <c r="G88" t="n">
-        <v>3.806966059646104e-07</v>
+        <v>2.379353787278815e-08</v>
       </c>
       <c r="H88" t="n">
-        <v>1.582517832535471e-13</v>
+        <v>9.890736453346691e-15</v>
       </c>
       <c r="I88" t="n">
-        <v>3.354993177725031e-12</v>
+        <v>2.096870736078145e-13</v>
       </c>
       <c r="J88" t="n">
-        <v>2.155959196864559e-06</v>
+        <v>1.34747449804035e-07</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0008600083855184984</v>
+        <v>5.375052409490615e-05</v>
       </c>
       <c r="L88" t="n">
-        <v>6.555026874082722e-09</v>
+        <v>4.096891796301701e-10</v>
       </c>
       <c r="M88" t="n">
-        <v>2.722592226316586e-12</v>
+        <v>1.701620141447866e-13</v>
       </c>
       <c r="N88" t="n">
-        <v>1.081337590531905e-07</v>
+        <v>6.758359940824408e-09</v>
       </c>
       <c r="O88" t="n">
-        <v>1.20031581527819e-05</v>
+        <v>7.501973845488686e-07</v>
       </c>
       <c r="P88" t="n">
-        <v>0.000198760622879121</v>
+        <v>1.242253892994506e-05</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.508672518227562e-12</v>
+        <v>9.429203238922264e-14</v>
       </c>
     </row>
     <row r="89">
@@ -5362,52 +5362,52 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.956320890344162e-08</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0001015458630971822</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>8.224121647306579e-10</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>4.768741780364006e-09</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4.877348140739609e-08</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>6.079512046857668e-15</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.069738042051727e-13</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1.078736705192326e-07</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0002644178241838998</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1.360630774769009e-10</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.751612825925613e-13</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.417166257946867e-08</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>7.984357046768597e-07</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.045130611567178e-05</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.857120273537783e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5417,52 +5417,52 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>8.181030903622693e-07</v>
+        <v>1.258620139018876e-07</v>
       </c>
       <c r="C91" t="n">
-        <v>3.9e-05</v>
+        <v>5.999999999999999e-06</v>
       </c>
       <c r="D91" t="n">
-        <v>0.007437796327069748</v>
+        <v>0.00114427635801073</v>
       </c>
       <c r="E91" t="n">
-        <v>6.258350693253103e-08</v>
+        <v>9.628231835774003e-09</v>
       </c>
       <c r="F91" t="n">
-        <v>7.872776807964465e-08</v>
+        <v>1.211196431994533e-08</v>
       </c>
       <c r="G91" t="n">
-        <v>9.274551755419332e-07</v>
+        <v>1.426854116218359e-07</v>
       </c>
       <c r="H91" t="n">
-        <v>4.345476715446036e-13</v>
+        <v>6.685348792993901e-14</v>
       </c>
       <c r="I91" t="n">
-        <v>9.344742279493297e-12</v>
+        <v>1.437652658383584e-12</v>
       </c>
       <c r="J91" t="n">
-        <v>5.873808933260912e-06</v>
+        <v>9.03662912809371e-07</v>
       </c>
       <c r="K91" t="n">
-        <v>0.001528655608954003</v>
+        <v>0.0002351777859929235</v>
       </c>
       <c r="L91" t="n">
-        <v>1.862827842056628e-08</v>
+        <v>2.865888987779428e-09</v>
       </c>
       <c r="M91" t="n">
-        <v>6.522354653238323e-12</v>
+        <v>1.00343917742128e-12</v>
       </c>
       <c r="N91" t="n">
-        <v>2.617580693779918e-07</v>
+        <v>4.027047221199873e-08</v>
       </c>
       <c r="O91" t="n">
-        <v>3.198307822757489e-05</v>
+        <v>4.92047357347306e-06</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0005009605510852711</v>
+        <v>7.707085401311862e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.697419473781405e-12</v>
+        <v>5.688337651971392e-13</v>
       </c>
     </row>
     <row r="92">
@@ -5527,52 +5527,52 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5.236547566946481e-08</v>
+        <v>1.745515855648827e-08</v>
       </c>
       <c r="C93" t="n">
-        <v>3e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0004387451580737943</v>
+        <v>0.0001462483860245981</v>
       </c>
       <c r="E93" t="n">
-        <v>3.865641355375319e-09</v>
+        <v>1.28854711845844e-09</v>
       </c>
       <c r="F93" t="n">
-        <v>5.533134485001897e-09</v>
+        <v>1.844378161667299e-09</v>
       </c>
       <c r="G93" t="n">
-        <v>5.659852889955158e-08</v>
+        <v>1.886617629985053e-08</v>
       </c>
       <c r="H93" t="n">
-        <v>2.250382065148348e-14</v>
+        <v>7.501273550494492e-15</v>
       </c>
       <c r="I93" t="n">
-        <v>6.081934960099281e-13</v>
+        <v>2.027311653366427e-13</v>
       </c>
       <c r="J93" t="n">
-        <v>1.887855776647864e-07</v>
+        <v>6.292852588826212e-08</v>
       </c>
       <c r="K93" t="n">
-        <v>6.802253959076956e-05</v>
+        <v>2.267417986358986e-05</v>
       </c>
       <c r="L93" t="n">
-        <v>9.39958059142983e-10</v>
+        <v>3.13319353047661e-10</v>
       </c>
       <c r="M93" t="n">
-        <v>4.752253882581559e-13</v>
+        <v>1.584084627527186e-13</v>
       </c>
       <c r="N93" t="n">
-        <v>2.074331148797766e-08</v>
+        <v>6.914437162659218e-09</v>
       </c>
       <c r="O93" t="n">
-        <v>3.212970439867161e-06</v>
+        <v>1.070990146622387e-06</v>
       </c>
       <c r="P93" t="n">
-        <v>4.231593828787005e-05</v>
+        <v>1.410531276262335e-05</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.269560508724663e-13</v>
+        <v>7.565201695748876e-14</v>
       </c>
     </row>
     <row r="94">
@@ -5692,52 +5692,52 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3.492969790666198e-06</v>
+        <v>7.322032894523644e-07</v>
       </c>
       <c r="C96" t="n">
-        <v>0.000291</v>
+        <v>6.100000000000001e-05</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0314585431908105</v>
+        <v>0.006594402524534158</v>
       </c>
       <c r="E96" t="n">
-        <v>2.515861655751391e-07</v>
+        <v>5.273799347107727e-08</v>
       </c>
       <c r="F96" t="n">
-        <v>4.655045721907253e-07</v>
+        <v>9.757999623242009e-08</v>
       </c>
       <c r="G96" t="n">
-        <v>4.604004407953412e-06</v>
+        <v>9.65100580361368e-07</v>
       </c>
       <c r="H96" t="n">
-        <v>1.547372400265238e-12</v>
+        <v>3.243632866535379e-13</v>
       </c>
       <c r="I96" t="n">
-        <v>3.310825881797855e-11</v>
+        <v>6.940219202394129e-12</v>
       </c>
       <c r="J96" t="n">
-        <v>3.306564382430423e-05</v>
+        <v>6.931286162483018e-06</v>
       </c>
       <c r="K96" t="n">
-        <v>0.005457435060391349</v>
+        <v>0.001143998414721211</v>
       </c>
       <c r="L96" t="n">
-        <v>8.209305432824123e-08</v>
+        <v>1.720850967018115e-08</v>
       </c>
       <c r="M96" t="n">
-        <v>3.302020417813493e-11</v>
+        <v>6.921761013286015e-12</v>
       </c>
       <c r="N96" t="n">
-        <v>1.44846943025539e-06</v>
+        <v>3.03631048953879e-07</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0003472946638132068</v>
+        <v>7.280059963094713e-05</v>
       </c>
       <c r="P96" t="n">
-        <v>0.004120418329385852</v>
+        <v>0.0008637303027234945</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.318174483542527e-11</v>
+        <v>6.955623487838287e-12</v>
       </c>
     </row>
     <row r="97">
@@ -5747,52 +5747,52 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9.211963595522891e-08</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>3e-06</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00122562578062575</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>2.505820719966927e-09</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>8.876126763056005e-09</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.181378362020809e-07</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1.334692222084155e-14</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>2.043205845662383e-13</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>2.838965333253913e-07</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>5.612598470502478e-05</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>5.52889984322185e-10</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.679772437591354e-13</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.116235840013984e-08</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.280200143315505e-06</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.265414407890505e-05</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.75745355978954e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5802,52 +5802,52 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.539003530640102</v>
+        <v>1.539009841079481</v>
       </c>
       <c r="C98" t="n">
-        <v>125.84319</v>
+        <v>125.843706</v>
       </c>
       <c r="D98" t="n">
-        <v>16664.25162123985</v>
+        <v>16664.31995035513</v>
       </c>
       <c r="E98" t="n">
-        <v>0.09097613093119068</v>
+        <v>0.09097650396435648</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2128066486258227</v>
+        <v>0.2128075212056634</v>
       </c>
       <c r="G98" t="n">
-        <v>2.237604745670744</v>
+        <v>2.237613920613375</v>
       </c>
       <c r="H98" t="n">
-        <v>5.252854240916184e-07</v>
+        <v>5.252875779410149e-07</v>
       </c>
       <c r="I98" t="n">
-        <v>9.830821638289877e-06</v>
+        <v>9.830861948011566e-06</v>
       </c>
       <c r="J98" t="n">
-        <v>10.48460086717467</v>
+        <v>10.48464385761418</v>
       </c>
       <c r="K98" t="n">
-        <v>2594.585724419801</v>
+        <v>2594.5963631062</v>
       </c>
       <c r="L98" t="n">
-        <v>0.02824816680576873</v>
+        <v>0.02824828263288717</v>
       </c>
       <c r="M98" t="n">
-        <v>1.279264971140055e-05</v>
+        <v>1.279270216562752e-05</v>
       </c>
       <c r="N98" t="n">
-        <v>0.7051117554682983</v>
+        <v>0.7051146466669862</v>
       </c>
       <c r="O98" t="n">
-        <v>89.03895485395174</v>
+        <v>89.03931994403492</v>
       </c>
       <c r="P98" t="n">
-        <v>1762.532220447589</v>
+        <v>1762.539447430835</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.223262489699137e-05</v>
+        <v>1.22326750549256e-05</v>
       </c>
     </row>
     <row r="99">
@@ -5857,52 +5857,52 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.216139919195797e-08</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0001311386249831481</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>7.157646440364867e-10</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1.685162307305057e-09</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>1.770552199025423e-08</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>4.324967063204682e-15</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>7.786306191166683e-14</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>8.290103749477811e-08</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>2.066984249984378e-05</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>2.219272418141677e-10</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1.011638291627848e-13</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.588316756871353e-09</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>7.039182933966949e-07</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.397731169530544e-05</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>9.672883137920769e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5912,52 +5912,52 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C100" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D100" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E100" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F100" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G100" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H100" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I100" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J100" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K100" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L100" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M100" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N100" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O100" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="101">
@@ -5967,52 +5967,52 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.409323166222129e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C101" t="n">
-        <v>3.6e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D101" t="n">
-        <v>0.001828171474614572</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E101" t="n">
-        <v>1.710362989812406e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F101" t="n">
-        <v>6.211850297148526e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G101" t="n">
-        <v>5.570862733341972e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H101" t="n">
-        <v>7.097631641043185e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I101" t="n">
-        <v>2.323653945198732e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J101" t="n">
-        <v>3.712273814225607e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K101" t="n">
-        <v>0.001058760411895507</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L101" t="n">
-        <v>1.086772402752104e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M101" t="n">
-        <v>5.510125227600784e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N101" t="n">
-        <v>2.074271907966545e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O101" t="n">
-        <v>3.626118746554389e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0004996046811824659</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.078542513735045e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="102">
@@ -6022,52 +6022,52 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C102" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D102" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E102" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F102" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G102" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H102" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I102" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J102" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K102" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L102" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M102" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N102" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O102" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P102" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="103">
@@ -6077,52 +6077,52 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C103" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D103" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E103" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F103" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G103" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H103" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I103" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J103" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K103" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L103" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M103" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N103" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O103" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P103" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="104">
@@ -6132,52 +6132,52 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C104" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D104" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E104" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F104" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G104" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H104" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I104" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J104" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K104" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L104" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M104" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N104" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O104" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P104" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="105">
@@ -6187,52 +6187,52 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C105" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D105" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E105" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F105" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G105" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H105" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I105" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J105" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K105" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L105" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M105" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N105" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O105" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="106">
@@ -6242,52 +6242,52 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.409323166222129e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C106" t="n">
-        <v>3.6e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D106" t="n">
-        <v>0.001828171474614572</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E106" t="n">
-        <v>1.710362989812406e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F106" t="n">
-        <v>6.211850297148526e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G106" t="n">
-        <v>5.570862733341972e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H106" t="n">
-        <v>7.097631641043185e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I106" t="n">
-        <v>2.323653945198732e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J106" t="n">
-        <v>3.712273814225607e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K106" t="n">
-        <v>0.001058760411895507</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L106" t="n">
-        <v>1.086772402752104e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M106" t="n">
-        <v>5.510125227600784e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N106" t="n">
-        <v>2.074271907966545e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O106" t="n">
-        <v>3.626118746554389e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P106" t="n">
-        <v>0.0004996046811824659</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.078542513735045e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="107">
@@ -6297,52 +6297,52 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.476248809728299e-07</v>
+        <v>4.015538610370217e-08</v>
       </c>
       <c r="C107" t="n">
-        <v>3.7e-05</v>
+        <v>6.000000000000002e-06</v>
       </c>
       <c r="D107" t="n">
-        <v>0.001878954015576087</v>
+        <v>0.0003046952457690954</v>
       </c>
       <c r="E107" t="n">
-        <v>1.75787307286275e-08</v>
+        <v>2.850604983020677e-09</v>
       </c>
       <c r="F107" t="n">
-        <v>6.384401694291539e-08</v>
+        <v>1.035308382858088e-08</v>
       </c>
       <c r="G107" t="n">
-        <v>5.725608920379248e-07</v>
+        <v>9.284771222236621e-08</v>
       </c>
       <c r="H107" t="n">
-        <v>7.294788075516605e-13</v>
+        <v>1.182938606840531e-13</v>
       </c>
       <c r="I107" t="n">
-        <v>2.388199888120919e-12</v>
+        <v>3.872756575331221e-13</v>
       </c>
       <c r="J107" t="n">
-        <v>3.81539253128743e-06</v>
+        <v>6.187123023709347e-07</v>
       </c>
       <c r="K107" t="n">
-        <v>0.001088170423337049</v>
+        <v>0.0001764600686492513</v>
       </c>
       <c r="L107" t="n">
-        <v>1.116960525050773e-09</v>
+        <v>1.811287337920173e-10</v>
       </c>
       <c r="M107" t="n">
-        <v>5.663184261700805e-12</v>
+        <v>9.183542046001309e-13</v>
       </c>
       <c r="N107" t="n">
-        <v>2.131890572076727e-07</v>
+        <v>3.45711984661091e-08</v>
       </c>
       <c r="O107" t="n">
-        <v>3.726844267292011e-05</v>
+        <v>6.043531244257317e-06</v>
       </c>
       <c r="P107" t="n">
-        <v>0.0005134825889930899</v>
+        <v>8.326744686374433e-05</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.164057583561018e-12</v>
+        <v>5.130904189558409e-13</v>
       </c>
     </row>
     <row r="108">
@@ -6352,52 +6352,52 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.09930930933541146</v>
+        <v>0.09762719351896301</v>
       </c>
       <c r="C108" t="n">
-        <v>14.838753</v>
+        <v>14.587412</v>
       </c>
       <c r="D108" t="n">
-        <v>753.5495820403167</v>
+        <v>740.7858474125084</v>
       </c>
       <c r="E108" t="n">
-        <v>0.007049903873935502</v>
+        <v>0.006930491556095934</v>
       </c>
       <c r="F108" t="n">
-        <v>0.02560447562010099</v>
+        <v>0.02517078321300777</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2296240447137955</v>
+        <v>0.2257346385741819</v>
       </c>
       <c r="H108" t="n">
-        <v>2.925555633511791e-07</v>
+        <v>2.876002138114807e-07</v>
       </c>
       <c r="I108" t="n">
-        <v>9.577813041744311e-07</v>
+        <v>9.415582623344257e-07</v>
       </c>
       <c r="J108" t="n">
-        <v>1.530153172157269</v>
+        <v>1.504235210692233</v>
       </c>
       <c r="K108" t="n">
-        <v>436.4078955082138</v>
+        <v>429.0159538224852</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0004479540903237496</v>
+        <v>0.0004403665774770797</v>
       </c>
       <c r="M108" t="n">
-        <v>2.2712052014288e-06</v>
+        <v>2.232735190739067e-06</v>
       </c>
       <c r="N108" t="n">
-        <v>0.08549891249209528</v>
+        <v>0.08405071922648355</v>
       </c>
       <c r="O108" t="n">
-        <v>14.9464112302195</v>
+        <v>14.69324669914235</v>
       </c>
       <c r="P108" t="n">
-        <v>205.9308461586211</v>
+        <v>202.442758931591</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.268936998925373e-06</v>
+        <v>1.247443555760243e-06</v>
       </c>
     </row>
     <row r="109">
@@ -6407,52 +6407,52 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.008944163852788165</v>
+        <v>0.009612476636276426</v>
       </c>
       <c r="C109" t="n">
-        <v>1.336433</v>
+        <v>1.436291999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>67.86746356482156</v>
+        <v>72.93855732269755</v>
       </c>
       <c r="E109" t="n">
-        <v>0.000634940428212212</v>
+        <v>0.0006823835220454553</v>
       </c>
       <c r="F109" t="n">
-        <v>0.002306033813380304</v>
+        <v>0.002478341913053346</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02068079109807892</v>
+        <v>0.02222607104721445</v>
       </c>
       <c r="H109" t="n">
-        <v>2.634863651926185e-08</v>
+        <v>2.831742095826998e-08</v>
       </c>
       <c r="I109" t="n">
-        <v>8.626132813732714e-08</v>
+        <v>9.270682145159377e-08</v>
       </c>
       <c r="J109" t="n">
-        <v>0.1378112563990825</v>
+        <v>0.148108588366159</v>
       </c>
       <c r="K109" t="n">
-        <v>39.30450982085413</v>
+        <v>42.24136415339505</v>
       </c>
       <c r="L109" t="n">
-        <v>4.034440284797784e-05</v>
+        <v>4.335895855260066e-05</v>
       </c>
       <c r="M109" t="n">
-        <v>2.045531441193944e-07</v>
+        <v>2.198374662055884e-07</v>
       </c>
       <c r="N109" t="n">
-        <v>0.007700348413276261</v>
+        <v>0.008275722631214122</v>
       </c>
       <c r="O109" t="n">
-        <v>1.346129098559423</v>
+        <v>1.446712596312804</v>
       </c>
       <c r="P109" t="n">
-        <v>18.54689396907574</v>
+        <v>19.93272796513683</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.142851613127352e-07</v>
+        <v>1.22824610670487e-07</v>
       </c>
     </row>
     <row r="110">
@@ -6462,52 +6462,52 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.351897998824639e-06</v>
+        <v>2.54317445323447e-07</v>
       </c>
       <c r="C110" t="n">
-        <v>0.000202</v>
+        <v>3.8e-05</v>
       </c>
       <c r="D110" t="n">
-        <v>0.01025807327422621</v>
+        <v>0.001929736556537604</v>
       </c>
       <c r="E110" t="n">
-        <v>9.59703677616961e-08</v>
+        <v>1.805383155913095e-08</v>
       </c>
       <c r="F110" t="n">
-        <v>3.485538222288895e-07</v>
+        <v>6.556953091434554e-08</v>
       </c>
       <c r="G110" t="n">
-        <v>3.125872978152995e-06</v>
+        <v>5.880355107416525e-07</v>
       </c>
       <c r="H110" t="n">
-        <v>3.98255997636312e-12</v>
+        <v>7.491944509990028e-13</v>
       </c>
       <c r="I110" t="n">
-        <v>1.303828047028177e-11</v>
+        <v>2.452745831043106e-12</v>
       </c>
       <c r="J110" t="n">
-        <v>2.082998084648813e-05</v>
+        <v>3.918511248349252e-06</v>
       </c>
       <c r="K110" t="n">
-        <v>0.005940822311191458</v>
+        <v>0.001117580434778591</v>
       </c>
       <c r="L110" t="n">
-        <v>6.098000704331248e-09</v>
+        <v>1.147148647349443e-09</v>
       </c>
       <c r="M110" t="n">
-        <v>3.091792488820439e-11</v>
+        <v>5.816243295800827e-12</v>
       </c>
       <c r="N110" t="n">
-        <v>1.163897015025673e-06</v>
+        <v>2.189509236186909e-07</v>
       </c>
       <c r="O110" t="n">
-        <v>0.0002034655518899963</v>
+        <v>3.827569788029633e-05</v>
       </c>
       <c r="P110" t="n">
-        <v>0.002803337377746058</v>
+        <v>0.000527360496803714</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.727404410484664e-11</v>
+        <v>3.249572653386991e-12</v>
       </c>
     </row>
     <row r="111">
@@ -6517,52 +6517,52 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.9870493998875473</v>
+        <v>1.095762672324327</v>
       </c>
       <c r="C111" t="n">
-        <v>147.484484</v>
+        <v>163.728373</v>
       </c>
       <c r="D111" t="n">
-        <v>7489.636849918034</v>
+        <v>8314.542808434851</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0700700008347722</v>
+        <v>0.077787485989278</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2544865377111658</v>
+        <v>0.2825155951310263</v>
       </c>
       <c r="G111" t="n">
-        <v>2.282266154616029</v>
+        <v>2.533634143156705</v>
       </c>
       <c r="H111" t="n">
-        <v>2.907751500559243e-06</v>
+        <v>3.228010224281447e-06</v>
       </c>
       <c r="I111" t="n">
-        <v>9.519525086172202e-06</v>
+        <v>1.056800221840054e-05</v>
       </c>
       <c r="J111" t="n">
-        <v>15.20841077660488</v>
+        <v>16.88345977037953</v>
       </c>
       <c r="K111" t="n">
-        <v>4337.5203618899</v>
+        <v>4815.253323235036</v>
       </c>
       <c r="L111" t="n">
-        <v>0.004452279640148171</v>
+        <v>0.004942652147886186</v>
       </c>
       <c r="M111" t="n">
-        <v>2.257383266578012e-05</v>
+        <v>2.506010662614809e-05</v>
       </c>
       <c r="N111" t="n">
-        <v>0.8497858945059483</v>
+        <v>0.9433810129193562</v>
       </c>
       <c r="O111" t="n">
-        <v>148.5545145161947</v>
+        <v>164.916256299486</v>
       </c>
       <c r="P111" t="n">
-        <v>2046.776072449458</v>
+        <v>2272.207266477468</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.261214594750767e-05</v>
+        <v>1.400124324958803e-05</v>
       </c>
     </row>
     <row r="112">
@@ -6572,52 +6572,52 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.005144969077615994</v>
+        <v>0.005203689637228306</v>
       </c>
       <c r="C112" t="n">
-        <v>0.768759</v>
+        <v>0.7775329999999997</v>
       </c>
       <c r="D112" t="n">
-        <v>39.03953540703399</v>
+        <v>39.48510142143031</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0003652380393569987</v>
+        <v>0.0003694065740438358</v>
       </c>
       <c r="F112" t="n">
-        <v>0.001326504395162667</v>
+        <v>0.001341644054747995</v>
       </c>
       <c r="G112" t="n">
-        <v>0.011896252400059</v>
+        <v>0.0120320267045655</v>
       </c>
       <c r="H112" t="n">
-        <v>1.515657834093533e-08</v>
+        <v>1.53295633965423e-08</v>
       </c>
       <c r="I112" t="n">
-        <v>4.962027453491755e-08</v>
+        <v>5.018660063811681e-08</v>
       </c>
       <c r="J112" t="n">
-        <v>0.07927344180972953</v>
+        <v>0.08017820543322994</v>
       </c>
       <c r="K112" t="n">
-        <v>22.60921098578829</v>
+        <v>22.86725442617637</v>
       </c>
       <c r="L112" t="n">
-        <v>2.32073907102029e-05</v>
+        <v>2.347226129525142e-05</v>
       </c>
       <c r="M112" t="n">
-        <v>1.176655099956986e-07</v>
+        <v>1.190084499608922e-07</v>
       </c>
       <c r="N112" t="n">
-        <v>0.004429486660267925</v>
+        <v>0.004480041276158198</v>
       </c>
       <c r="O112" t="n">
-        <v>0.7743365059673348</v>
+        <v>0.7831741631568535</v>
       </c>
       <c r="P112" t="n">
-        <v>10.66876653058753</v>
+        <v>10.79053129371795</v>
       </c>
       <c r="Q112" t="n">
-        <v>6.574047956434552e-08</v>
+        <v>6.64907887869986e-08</v>
       </c>
     </row>
     <row r="113">
